--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.9%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.8%</t>
+          <t>-596.1%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.0%</t>
+          <t>-270.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-261.6%</t>
+          <t>-271.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-212.2%</t>
+          <t>-220.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.0%</t>
+          <t>-163.7%</t>
         </is>
       </c>
     </row>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.390747721418348</v>
+        <v>-4.315911056361395</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.046119591322908</v>
+        <v>1.076054257345689</v>
       </c>
       <c r="F1940" t="n">
         <v>0.02534968339819066</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.593774298961582</v>
+        <v>-4.518937633904629</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.96804034552552</v>
+        <v>0.9979750115483013</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1776768941450427</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.435848700026289</v>
+        <v>-4.361012034969336</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.04138297153177</v>
+        <v>1.071317637554551</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1776768941450427</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.349605236999911</v>
+        <v>-4.274768571942958</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.070826627316181</v>
+        <v>1.100761293338962</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1776768941450427</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.350788321650972</v>
+        <v>-4.275951656594019</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.062129168900282</v>
+        <v>1.092063834923063</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1833199426115543</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.227660614656889</v>
+        <v>-4.152823949599936</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.111932124731017</v>
+        <v>1.141866790753798</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1833199426115543</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.134850133206029</v>
+        <v>-4.060013468149076</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.078329009202726</v>
+        <v>1.108263675225508</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.09050946116069492</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.086287080985</v>
+        <v>-4.011450415928047</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.099627706015739</v>
+        <v>1.12956237203852</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.04194640893966473</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.973615862748749</v>
+        <v>-3.898779197691796</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.139771901821962</v>
+        <v>1.169706567844743</v>
       </c>
       <c r="F1948" t="n">
         <v>0.07072480929658548</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.861238861566077</v>
+        <v>-3.786402196509124</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.190213998125698</v>
+        <v>1.22014866414848</v>
       </c>
       <c r="F1949" t="n">
         <v>0.07072480929658548</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.059473430452807</v>
+        <v>-3.984636765395854</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.122417372339545</v>
+        <v>1.152352038362326</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1275097595901451</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.142474711478086</v>
+        <v>-4.067638046421133</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9275725799300869</v>
+        <v>0.9575072459528682</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1460806441173189</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.269541717785074</v>
+        <v>-4.194705052728121</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9968954381264974</v>
+        <v>1.026830104149278</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1460806441173189</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.356140300766177</v>
+        <v>-4.281303635709224</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9767690310363792</v>
+        <v>1.00670369705916</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1460806441173189</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.317756638208026</v>
+        <v>-4.242919973151073</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9895419374020082</v>
+        <v>1.01947660342479</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1076969815591677</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.14064030817286</v>
+        <v>-4.065803643115907</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.057117498261377</v>
+        <v>1.087052164284158</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1076969815591677</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.110938184196566</v>
+        <v>-4.036101519139613</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.069681739613807</v>
+        <v>1.099616405636588</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1121671067744811</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.931562762957799</v>
+        <v>-3.856726097900846</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.135218883415729</v>
+        <v>1.16515354943851</v>
       </c>
       <c r="F1957" t="n">
         <v>0.04460965139623763</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.976576976478405</v>
+        <v>-3.901740311421452</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.098020653339076</v>
+        <v>1.127955319361857</v>
       </c>
       <c r="F1958" t="n">
         <v>0.01426075608163302</v>
@@ -46608,10 +46608,10 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.24358148675084</v>
+        <v>-4.168744821693887</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9969104115690475</v>
+        <v>1.026845077591829</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1801022819613156</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.532368707209756</v>
+        <v>-4.457532042152803</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8805994452819828</v>
+        <v>0.910534111304764</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2811884020603159</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.499893121038983</v>
+        <v>-4.42505645598203</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8911896413046083</v>
+        <v>0.9211243073273896</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2811884020603159</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.480854993331686</v>
+        <v>-4.406018328274733</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8953296115957723</v>
+        <v>0.9252642776185533</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3393720133915105</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.511981624482305</v>
+        <v>-4.437144959425352</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.060460828074205</v>
+        <v>1.090395494096987</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3393720133915105</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.564302005083096</v>
+        <v>-4.489465340026143</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.040366004820022</v>
+        <v>1.070300670842804</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3044251533826383</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.708624911008015</v>
+        <v>-4.633788245951062</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9886453728469806</v>
+        <v>1.018580038869762</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3044251533826383</v>
@@ -46769,10 +46769,10 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.560881940773013</v>
+        <v>-4.48604527571606</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.126895208733004</v>
+        <v>1.156829874755785</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1366177961477552</v>
@@ -46792,10 +46792,10 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.662896623304234</v>
+        <v>-4.588059958247281</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.088882957251996</v>
+        <v>1.118817623274777</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1366177961477552</v>
@@ -46815,10 +46815,10 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.526287279210141</v>
+        <v>-4.451450614153188</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.144189043281292</v>
+        <v>1.174123709304073</v>
       </c>
       <c r="F1968" t="n">
         <v>-8.452053662677539e-06</v>
@@ -46838,10 +46838,10 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.669052612032791</v>
+        <v>-4.594215946975838</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.086163386892342</v>
+        <v>1.116098052915123</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.1427737848763131</v>
@@ -46861,10 +46861,10 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.606754613256669</v>
+        <v>-4.531917948199716</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.177418140199612</v>
+        <v>1.207352806222393</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.1427737848763131</v>
@@ -46884,10 +46884,10 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.404964415591511</v>
+        <v>-4.330127750534558</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9667150916550726</v>
+        <v>0.9966497576778539</v>
       </c>
       <c r="F1971" t="n">
         <v>0.0552444072928413</v>
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.760988493069022</v>
+        <v>3.834433094882855</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.342011338169972</v>
+        <v>-4.34568986686915</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.062186554945864</v>
+        <v>1.060715143466192</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1181974847143797</v>
+        <v>0.0396822909582491</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.870266005356228</v>
+        <v>2.823156889102549</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-596.1%</t>
+          <t>-597.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.2%</t>
+          <t>-270.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-271.3%</t>
+          <t>-275.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-220.0%</t>
+          <t>-212.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-163.7%</t>
+          <t>-159.2%</t>
         </is>
       </c>
     </row>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.928914901679625</v>
+        <v>-4.946500249596268</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9871727094068388</v>
+        <v>0.9801385702401815</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3669885755056136</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.708894103642614</v>
+        <v>-4.726479451559258</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.076760065632257</v>
+        <v>1.0697259264656</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2257687304376333</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.576026414579337</v>
+        <v>-4.59361176249598</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.145801324059392</v>
+        <v>1.138767184892734</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2257687304376333</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.416511311059967</v>
+        <v>-4.43409665897661</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.210753209907441</v>
+        <v>1.203719070740784</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.06625362691826342</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.27183916596023</v>
+        <v>-4.289424513876873</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.278710170508776</v>
+        <v>1.271676031342119</v>
       </c>
       <c r="F1932" t="n">
         <v>0.078418518181474</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.331713993317922</v>
+        <v>-4.349299341234565</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.240797730967125</v>
+        <v>1.233763591800468</v>
       </c>
       <c r="F1933" t="n">
         <v>0.01854369082378188</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.244914495538913</v>
+        <v>-4.262499843455556</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.297918023401295</v>
+        <v>1.290883884234638</v>
       </c>
       <c r="F1934" t="n">
         <v>0.01854369082378188</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.247384202000719</v>
+        <v>-4.264969549917362</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.297002542189985</v>
+        <v>1.289968403023327</v>
       </c>
       <c r="F1935" t="n">
         <v>0.01607398436197571</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.315754388324729</v>
+        <v>-4.333339736241372</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.280661390135083</v>
+        <v>1.273627250968425</v>
       </c>
       <c r="F1936" t="n">
         <v>0.02534968339819066</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.424292569240863</v>
+        <v>-4.441877917157506</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.22768282640052</v>
+        <v>1.220648687233863</v>
       </c>
       <c r="F1937" t="n">
         <v>0.02534968339819066</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.455285728569568</v>
+        <v>-4.472871076486212</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.039995127709425</v>
+        <v>1.032960988542768</v>
       </c>
       <c r="F1938" t="n">
         <v>0.02534968339819066</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.279811468777099</v>
+        <v>-4.297396816693743</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.1147520636182</v>
+        <v>1.107717924451543</v>
       </c>
       <c r="F1939" t="n">
         <v>0.02534968339819066</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.315911056361395</v>
+        <v>-4.408333069334992</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.076054257345689</v>
+        <v>1.03908545215625</v>
       </c>
       <c r="F1940" t="n">
         <v>0.02534968339819066</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.518937633904629</v>
+        <v>-4.611359646878225</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9979750115483013</v>
+        <v>0.9610062063588627</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1776768941450427</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.361012034969336</v>
+        <v>-4.453434047942932</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.071317637554551</v>
+        <v>1.034348832365112</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1776768941450427</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.274768571942958</v>
+        <v>-4.367190584916554</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.100761293338962</v>
+        <v>1.063792488149524</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1776768941450427</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.275951656594019</v>
+        <v>-4.368373669567616</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.092063834923063</v>
+        <v>1.055095029733625</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1833199426115543</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.152823949599936</v>
+        <v>-4.245245962573533</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.141866790753798</v>
+        <v>1.104897985564359</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1833199426115543</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.060013468149076</v>
+        <v>-4.152435481122673</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.108263675225508</v>
+        <v>1.071294870036069</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.09050946116069492</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.011450415928047</v>
+        <v>-4.103872428901643</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.12956237203852</v>
+        <v>1.092593566849082</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.04194640893966473</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.898779197691796</v>
+        <v>-3.991201210665393</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.169706567844743</v>
+        <v>1.132737762655305</v>
       </c>
       <c r="F1948" t="n">
         <v>0.07072480929658548</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.786402196509124</v>
+        <v>-3.87882420948272</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22014866414848</v>
+        <v>1.183179858959041</v>
       </c>
       <c r="F1949" t="n">
         <v>0.07072480929658548</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.984636765395854</v>
+        <v>-4.077058778369451</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.152352038362326</v>
+        <v>1.115383233172888</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1275097595901451</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.067638046421133</v>
+        <v>-4.16006005939473</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9575072459528682</v>
+        <v>0.9205384407634296</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1460806441173189</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.194705052728121</v>
+        <v>-4.287127065701718</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.026830104149278</v>
+        <v>0.9898612989598399</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1460806441173189</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.281303635709224</v>
+        <v>-4.373725648682821</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.00670369705916</v>
+        <v>0.9697348918697217</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1460806441173189</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.242919973151073</v>
+        <v>-4.33534198612467</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.01947660342479</v>
+        <v>0.9825077982353509</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1076969815591677</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.065803643115907</v>
+        <v>-4.158225656089503</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.087052164284158</v>
+        <v>1.050083359094719</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1076969815591677</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.036101519139613</v>
+        <v>-4.12852353211321</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.099616405636588</v>
+        <v>1.06264760044715</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1121671067744811</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.856726097900846</v>
+        <v>-3.949148110874442</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.16515354943851</v>
+        <v>1.128184744249071</v>
       </c>
       <c r="F1957" t="n">
         <v>0.04460965139623763</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.901740311421452</v>
+        <v>-3.994162324395048</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.127955319361857</v>
+        <v>1.090986514172418</v>
       </c>
       <c r="F1958" t="n">
         <v>0.01426075608163302</v>
@@ -46608,10 +46608,10 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.168744821693887</v>
+        <v>-4.261166834667484</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.026845077591829</v>
+        <v>0.9898762724023902</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1801022819613156</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.457532042152803</v>
+        <v>-4.549954055126399</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.910534111304764</v>
+        <v>0.8735653061153255</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2811884020603159</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.42505645598203</v>
+        <v>-4.517478468955627</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9211243073273896</v>
+        <v>0.884155502137951</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2811884020603159</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.406018328274733</v>
+        <v>-4.49844034124833</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9252642776185533</v>
+        <v>0.8882954724291148</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3393720133915105</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.437144959425352</v>
+        <v>-4.529566972398948</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.090395494096987</v>
+        <v>1.053426688907548</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3393720133915105</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.489465340026143</v>
+        <v>-4.58188735299974</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.070300670842804</v>
+        <v>1.033331865653365</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3044251533826383</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.633788245951062</v>
+        <v>-4.726210258924659</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.018580038869762</v>
+        <v>0.9816112336803233</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3044251533826383</v>
@@ -46769,10 +46769,10 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.48604527571606</v>
+        <v>-4.578467288689656</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.156829874755785</v>
+        <v>1.119861069566346</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1366177961477552</v>
@@ -46792,10 +46792,10 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.588059958247281</v>
+        <v>-4.680481971220877</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.118817623274777</v>
+        <v>1.081848818085339</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1366177961477552</v>
@@ -46815,10 +46815,10 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.451450614153188</v>
+        <v>-4.543872627126785</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.174123709304073</v>
+        <v>1.137154904114634</v>
       </c>
       <c r="F1968" t="n">
         <v>-8.452053662677539e-06</v>
@@ -46838,10 +46838,10 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.594215946975838</v>
+        <v>-4.686637959949435</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.116098052915123</v>
+        <v>1.079129247725684</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.1427737848763131</v>
@@ -46861,10 +46861,10 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.531917948199716</v>
+        <v>-4.624339961173312</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.207352806222393</v>
+        <v>1.170384001032954</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.1427737848763131</v>
@@ -46884,10 +46884,10 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.330127750534558</v>
+        <v>-4.422549763508155</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9966497576778539</v>
+        <v>0.9596809524884153</v>
       </c>
       <c r="F1971" t="n">
         <v>0.0552444072928413</v>
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.834433094882855</v>
+        <v>3.806817340231198</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.34568986686915</v>
+        <v>-4.362659081865561</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.060715143466192</v>
+        <v>1.053927457467628</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.0396822909582491</v>
+        <v>0.1151350889354348</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.823156889102549</v>
+        <v>2.868428567888861</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>25.1%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-51.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>446.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-597.8%</t>
+          <t>-612.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.8%</t>
+          <t>-276.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-275.5%</t>
+          <t>-257.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-212.5%</t>
+          <t>-228.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.2%</t>
+          <t>-168.9%</t>
         </is>
       </c>
     </row>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972331</v>
+        <v>3.84861305097233</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.946500249596268</v>
+        <v>-4.928914901679625</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9801385702401815</v>
+        <v>0.9871727094068388</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3669885755056136</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614593</v>
+        <v>3.818665376145929</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.726479451559258</v>
+        <v>-4.708894103642614</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.0697259264656</v>
+        <v>1.076760065632257</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2257687304376333</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009942</v>
+        <v>3.843270952009941</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.59361176249598</v>
+        <v>-4.576026414579337</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.138767184892734</v>
+        <v>1.145801324059392</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2257687304376333</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.43409665897661</v>
+        <v>-4.416511311059967</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.203719070740784</v>
+        <v>1.210753209907441</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.06625362691826342</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.289424513876873</v>
+        <v>-4.27183916596023</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.271676031342119</v>
+        <v>1.278710170508776</v>
       </c>
       <c r="F1932" t="n">
         <v>0.078418518181474</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.349299341234565</v>
+        <v>-4.331713993317922</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.233763591800468</v>
+        <v>1.240797730967125</v>
       </c>
       <c r="F1933" t="n">
         <v>0.01854369082378188</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.262499843455556</v>
+        <v>-4.244914495538913</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290883884234638</v>
+        <v>1.297918023401295</v>
       </c>
       <c r="F1934" t="n">
         <v>0.01854369082378188</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.264969549917362</v>
+        <v>-4.247384202000719</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.289968403023327</v>
+        <v>1.297002542189985</v>
       </c>
       <c r="F1935" t="n">
         <v>0.01607398436197571</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.333339736241372</v>
+        <v>-4.315754388324729</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.273627250968425</v>
+        <v>1.280661390135083</v>
       </c>
       <c r="F1936" t="n">
         <v>0.02534968339819066</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978362</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.441877917157506</v>
+        <v>-4.424292569240863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.220648687233863</v>
+        <v>1.22768282640052</v>
       </c>
       <c r="F1937" t="n">
         <v>0.02534968339819066</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887695</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.472871076486212</v>
+        <v>-4.455285728569568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.032960988542768</v>
+        <v>1.039995127709425</v>
       </c>
       <c r="F1938" t="n">
         <v>0.02534968339819066</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.74603895067589</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.297396816693743</v>
+        <v>-4.279811468777099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.107717924451543</v>
+        <v>1.1147520636182</v>
       </c>
       <c r="F1939" t="n">
         <v>0.02534968339819066</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695436</v>
+        <v>3.765020747695434</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.408333069334992</v>
+        <v>-4.390747721418348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.03908545215625</v>
+        <v>1.046119591322908</v>
       </c>
       <c r="F1940" t="n">
         <v>0.02534968339819066</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.611359646878225</v>
+        <v>-4.593774298961582</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9610062063588627</v>
+        <v>0.96804034552552</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1776768941450427</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734155</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.453434047942932</v>
+        <v>-4.435848700026289</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.034348832365112</v>
+        <v>1.04138297153177</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1776768941450427</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.367190584916554</v>
+        <v>-4.349605236999911</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.063792488149524</v>
+        <v>1.070826627316181</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1776768941450427</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786039</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.368373669567616</v>
+        <v>-4.350788321650972</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.055095029733625</v>
+        <v>1.062129168900282</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1833199426115543</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.245245962573533</v>
+        <v>-4.227660614656889</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.104897985564359</v>
+        <v>1.111932124731017</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1833199426115543</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.152435481122673</v>
+        <v>-4.134850133206029</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.071294870036069</v>
+        <v>1.078329009202726</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.09050946116069492</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.103872428901643</v>
+        <v>-4.086287080985</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.092593566849082</v>
+        <v>1.099627706015739</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.04194640893966473</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.991201210665393</v>
+        <v>-3.973615862748749</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.132737762655305</v>
+        <v>1.139771901821962</v>
       </c>
       <c r="F1948" t="n">
         <v>0.07072480929658548</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268532</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.87882420948272</v>
+        <v>-3.861238861566077</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.183179858959041</v>
+        <v>1.190213998125698</v>
       </c>
       <c r="F1949" t="n">
         <v>0.07072480929658548</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.689594264968857</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.077058778369451</v>
+        <v>-4.059473430452807</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.115383233172888</v>
+        <v>1.122417372339545</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1275097595901451</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175318</v>
+        <v>3.643066046175317</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.16006005939473</v>
+        <v>-4.142474711478086</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9205384407634296</v>
+        <v>0.9275725799300869</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1460806441173189</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199263</v>
+        <v>3.682712735199261</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.287127065701718</v>
+        <v>-4.269541717785074</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9898612989598399</v>
+        <v>0.9968954381264974</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1460806441173189</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660762</v>
+        <v>3.73300886566076</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.373725648682821</v>
+        <v>-4.356140300766177</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9697348918697217</v>
+        <v>0.9767690310363792</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1460806441173189</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383417</v>
+        <v>3.741170494383415</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.33534198612467</v>
+        <v>-4.317756638208026</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9825077982353509</v>
+        <v>0.9895419374020082</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1076969815591677</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002478</v>
+        <v>3.751143622002476</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.158225656089503</v>
+        <v>-4.14064030817286</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.050083359094719</v>
+        <v>1.057117498261377</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1076969815591677</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263895</v>
+        <v>3.741324873263893</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.12852353211321</v>
+        <v>-4.110938184196566</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.06264760044715</v>
+        <v>1.069681739613807</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1121671067744811</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481227</v>
+        <v>3.750725801481225</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.949148110874442</v>
+        <v>-3.931562762957799</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.128184744249071</v>
+        <v>1.135218883415729</v>
       </c>
       <c r="F1957" t="n">
         <v>0.04460965139623763</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452222</v>
+        <v>3.716988143452221</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.994162324395048</v>
+        <v>-3.976576976478405</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.090986514172418</v>
+        <v>1.098020653339076</v>
       </c>
       <c r="F1958" t="n">
         <v>0.01426075608163302</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.737023032979527</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.261166834667484</v>
+        <v>-4.24358148675084</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9898762724023902</v>
+        <v>0.9969104115690475</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1801022819613156</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230803</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.549954055126399</v>
+        <v>-4.532368707209756</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8735653061153255</v>
+        <v>0.8805994452819828</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2811884020603159</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285449</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.517478468955627</v>
+        <v>-4.499893121038983</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.884155502137951</v>
+        <v>0.8911896413046083</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2811884020603159</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.709506867848097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.49844034124833</v>
+        <v>-4.480854993331686</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8882954724291148</v>
+        <v>0.8953296115957723</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3393720133915105</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.529566972398948</v>
+        <v>-4.511981624482305</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.053426688907548</v>
+        <v>1.060460828074205</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3393720133915105</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537861</v>
+        <v>3.722443786537859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.58188735299974</v>
+        <v>-4.564302005083096</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.033331865653365</v>
+        <v>1.040366004820022</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3044251533826383</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259117</v>
+        <v>3.787422005259115</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.726210258924659</v>
+        <v>-4.708624911008015</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9816112336803233</v>
+        <v>0.9886453728469806</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3044251533826383</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989902</v>
+        <v>3.7814976749899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.578467288689656</v>
+        <v>-4.560881940773013</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.119861069566346</v>
+        <v>1.126895208733004</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1366177961477552</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651163</v>
+        <v>3.802242353651161</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.680481971220877</v>
+        <v>-4.662896623304234</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.081848818085339</v>
+        <v>1.088882957251996</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1366177961477552</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864722</v>
+        <v>3.80560540986472</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.543872627126785</v>
+        <v>-4.688318067215689</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.137154904114634</v>
+        <v>1.079376728079072</v>
       </c>
       <c r="F1968" t="n">
-        <v>-8.452053662677539e-06</v>
+        <v>-0.1620392400592104</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.955055308046898</v>
+        <v>2.857836835243569</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360609</v>
+        <v>3.798236219360607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.686637959949435</v>
+        <v>-4.831083400038339</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.079129247725684</v>
+        <v>1.021351071690123</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1427737848763131</v>
+        <v>-0.3048045728818608</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.868476585093418</v>
+        <v>2.771258112290089</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86735906126842</v>
+        <v>3.867359061268418</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.624339961173312</v>
+        <v>-4.768785401262217</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.170384001032954</v>
+        <v>1.112605824997392</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1427737848763131</v>
+        <v>-0.3048045728818608</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.934812138890239</v>
+        <v>2.83759366608691</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462184</v>
+        <v>3.848725564462182</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.422549763508155</v>
+        <v>-4.566995203597059</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9596809524884153</v>
+        <v>0.9019027764528538</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.0552444072928413</v>
+        <v>-0.1067863807127064</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.76220392658113</v>
+        <v>2.664985453777801</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.806817340231198</v>
+        <v>3.531315637153878</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.362659081865561</v>
+        <v>-4.507104521954465</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.053927457467628</v>
+        <v>0.9961492814320663</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1151350889354348</v>
+        <v>-0.04689569907011293</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.868428567888861</v>
+        <v>2.771210095085532</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-37.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.0%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-612.3%</t>
+          <t>-590.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,42 +1155,42 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>46.1%</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-0.0%</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.6%</t>
+          <t>-267.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-257.9%</t>
+          <t>-275.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-228.7%</t>
+          <t>-212.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.9%</t>
+          <t>-172.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1972"/>
+  <dimension ref="A1:G1973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776671</v>
+        <v>3.500446096776674</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781941</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567235</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487764</v>
+        <v>3.789307536487766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309717</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858719</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096464</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255782</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749179</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102774</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353066</v>
+        <v>3.764614304353068</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544775</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712285</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837675</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349957</v>
+        <v>3.822323422349959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097233</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.928914901679625</v>
+        <v>-4.946220878224191</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9871727094068388</v>
+        <v>0.9802503187890126</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3669885755056136</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145929</v>
+        <v>3.818665376145933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.708894103642614</v>
+        <v>-4.72620008018718</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.076760065632257</v>
+        <v>1.069837675014431</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2257687304376333</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009941</v>
+        <v>3.843270952009945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.576026414579337</v>
+        <v>-4.593332391123902</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.145801324059392</v>
+        <v>1.138878933441565</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2257687304376333</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.416511311059967</v>
+        <v>-4.433817287604533</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.210753209907441</v>
+        <v>1.203830819289615</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.06625362691826342</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.27183916596023</v>
+        <v>-4.289145142504795</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.278710170508776</v>
+        <v>1.27178777989095</v>
       </c>
       <c r="F1932" t="n">
         <v>0.078418518181474</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.331713993317922</v>
+        <v>-4.349019969862487</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.240797730967125</v>
+        <v>1.233875340349299</v>
       </c>
       <c r="F1933" t="n">
         <v>0.01854369082378188</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.244914495538913</v>
+        <v>-4.262220472083479</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.297918023401295</v>
+        <v>1.290995632783468</v>
       </c>
       <c r="F1934" t="n">
         <v>0.01854369082378188</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.247384202000719</v>
+        <v>-4.264690178545285</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.297002542189985</v>
+        <v>1.290080151572158</v>
       </c>
       <c r="F1935" t="n">
         <v>0.01607398436197571</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.315754388324729</v>
+        <v>-4.333060364869295</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.280661390135083</v>
+        <v>1.273738999517256</v>
       </c>
       <c r="F1936" t="n">
         <v>0.02534968339819066</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978362</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.424292569240863</v>
+        <v>-4.441598545785429</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.22768282640052</v>
+        <v>1.220760435782694</v>
       </c>
       <c r="F1937" t="n">
         <v>0.02534968339819066</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887695</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.455285728569568</v>
+        <v>-4.472591705114135</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.039995127709425</v>
+        <v>1.033072737091598</v>
       </c>
       <c r="F1938" t="n">
         <v>0.02534968339819066</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.74603895067589</v>
+        <v>3.746038950675893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.279811468777099</v>
+        <v>-4.297117445321666</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.1147520636182</v>
+        <v>1.107829673000374</v>
       </c>
       <c r="F1939" t="n">
         <v>0.02534968339819066</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695434</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.390747721418348</v>
+        <v>-4.333217032905962</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.046119591322908</v>
+        <v>1.069131866727862</v>
       </c>
       <c r="F1940" t="n">
         <v>0.02534968339819066</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.593774298961582</v>
+        <v>-4.536243610449195</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.96804034552552</v>
+        <v>0.9910526209304746</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1776768941450427</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734155</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.435848700026289</v>
+        <v>-4.378318011513902</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.04138297153177</v>
+        <v>1.064395246936724</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1776768941450427</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.349605236999911</v>
+        <v>-4.292074548487524</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.070826627316181</v>
+        <v>1.093838902721135</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1776768941450427</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786039</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.350788321650972</v>
+        <v>-4.293257633138586</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.062129168900282</v>
+        <v>1.085141444305237</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1833199426115543</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.227660614656889</v>
+        <v>-4.170129926144503</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.111932124731017</v>
+        <v>1.134944400135971</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1833199426115543</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.134850133206029</v>
+        <v>-4.077319444693643</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.078329009202726</v>
+        <v>1.101341284607681</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.09050946116069492</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030422</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.086287080985</v>
+        <v>-4.028756392472613</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.099627706015739</v>
+        <v>1.122639981420694</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.04194640893966473</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942734</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.973615862748749</v>
+        <v>-3.916085174236363</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.139771901821962</v>
+        <v>1.162784177226917</v>
       </c>
       <c r="F1948" t="n">
         <v>0.07072480929658548</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268532</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.861238861566077</v>
+        <v>-3.80370817305369</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.190213998125698</v>
+        <v>1.213226273530653</v>
       </c>
       <c r="F1949" t="n">
         <v>0.07072480929658548</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968857</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.059473430452807</v>
+        <v>-4.001942741940421</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.122417372339545</v>
+        <v>1.1454296477445</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1275097595901451</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175317</v>
+        <v>3.64306604617532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.142474711478086</v>
+        <v>-4.0849440229657</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9275725799300869</v>
+        <v>0.9505848553350416</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1460806441173189</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199261</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.269541717785074</v>
+        <v>-4.212011029272688</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9968954381264974</v>
+        <v>1.019907713531452</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1460806441173189</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566076</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.356140300766177</v>
+        <v>-4.298609612253791</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9767690310363792</v>
+        <v>0.9997813064413337</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1460806441173189</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383415</v>
+        <v>3.741170494383419</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.317756638208026</v>
+        <v>-4.26022594969564</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9895419374020082</v>
+        <v>1.012554212806963</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1076969815591677</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002476</v>
+        <v>3.75114362200248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.14064030817286</v>
+        <v>-4.083109619660473</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.057117498261377</v>
+        <v>1.080129773666331</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1076969815591677</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263893</v>
+        <v>3.741324873263896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.110938184196566</v>
+        <v>-4.05340749568418</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.069681739613807</v>
+        <v>1.092694015018762</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1121671067744811</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481225</v>
+        <v>3.750725801481229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.931562762957799</v>
+        <v>-3.874032074445412</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.135218883415729</v>
+        <v>1.158231158820683</v>
       </c>
       <c r="F1957" t="n">
         <v>0.04460965139623763</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452221</v>
+        <v>3.716988143452225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.976576976478405</v>
+        <v>-3.919046287966018</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.098020653339076</v>
+        <v>1.121032928744031</v>
       </c>
       <c r="F1958" t="n">
         <v>0.01426075608163302</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979527</v>
+        <v>3.737023032979532</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.24358148675084</v>
+        <v>-4.186050798238454</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9969104115690475</v>
+        <v>1.019922686974002</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1801022819613156</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230803</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.532368707209756</v>
+        <v>-4.474838018697369</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8805994452819828</v>
+        <v>0.9036117206869374</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2811884020603159</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285449</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.499893121038983</v>
+        <v>-4.442362432526597</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8911896413046083</v>
+        <v>0.914201916709563</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2811884020603159</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848097</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.480854993331686</v>
+        <v>-4.4233243048193</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8953296115957723</v>
+        <v>0.9183418870007269</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3393720133915105</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601248</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.511981624482305</v>
+        <v>-4.454450935969918</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.060460828074205</v>
+        <v>1.08347310347916</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3393720133915105</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537859</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.564302005083096</v>
+        <v>-4.50677131657071</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.040366004820022</v>
+        <v>1.063378280224977</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3044251533826383</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259115</v>
+        <v>3.787422005259119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.708624911008015</v>
+        <v>-4.651094222495629</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9886453728469806</v>
+        <v>1.011657648251935</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3044251533826383</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.7814976749899</v>
+        <v>3.781497674989904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.560881940773013</v>
+        <v>-4.503351252260626</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.126895208733004</v>
+        <v>1.149907484137958</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1366177961477552</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651161</v>
+        <v>3.802242353651166</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.662896623304234</v>
+        <v>-4.605365934791847</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.088882957251996</v>
+        <v>1.111895232656951</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1366177961477552</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560540986472</v>
+        <v>3.805605409864725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.688318067215689</v>
+        <v>-4.468756590697755</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.079376728079072</v>
+        <v>1.167201318686246</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1620392400592104</v>
+        <v>-8.452053662677539e-06</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.857836835243569</v>
+        <v>2.955055308046898</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360607</v>
+        <v>3.798236219360612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.831083400038339</v>
+        <v>-4.611521923520405</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.021351071690123</v>
+        <v>1.109175662297296</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3048045728818608</v>
+        <v>-0.1427737848763131</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.771258112290089</v>
+        <v>2.868476585093418</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268418</v>
+        <v>3.867359061268422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.768785401262217</v>
+        <v>-4.549223924744282</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.112605824997392</v>
+        <v>1.200430415604566</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3048045728818608</v>
+        <v>-0.1427737848763131</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.83759366608691</v>
+        <v>2.934812138890239</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462182</v>
+        <v>3.848725564462185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.566995203597059</v>
+        <v>-4.347433727079125</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9019027764528538</v>
+        <v>0.9897273670600273</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1067863807127064</v>
+        <v>0.0552444072928413</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.664985453777801</v>
+        <v>2.76220392658113</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,45 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.531315637153878</v>
+        <v>3.841441242322409</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.507104521954465</v>
+        <v>-4.287543045436531</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9961492814320663</v>
+        <v>1.08397387203924</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.04689569907011293</v>
+        <v>0.1151350889354348</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.771210095085532</v>
+        <v>2.868428567888861</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="2" t="n">
+        <v>45435</v>
+      </c>
+      <c r="B1973" t="n">
+        <v>3.806563277902788</v>
+      </c>
+      <c r="C1973" t="n">
+        <v>2.746637071339096</v>
+      </c>
+      <c r="D1973" t="n">
+        <v>-4.287543045436531</v>
+      </c>
+      <c r="E1973" t="n">
+        <v>1.08397387203924</v>
+      </c>
+      <c r="F1973" t="n">
+        <v>0.1151350889354348</v>
+      </c>
+      <c r="G1973" t="n">
+        <v>2.739700868325464</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>448.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-590.3%</t>
+          <t>-620.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-267.8%</t>
+          <t>-279.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-275.5%</t>
+          <t>-257.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-212.5%</t>
+          <t>-228.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-172.1%</t>
+          <t>-176.4%</t>
         </is>
       </c>
     </row>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.45013784647568</v>
+        <v>-8.533255825547851</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2672757126158296</v>
+        <v>-0.3005229042446977</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.833139235218312</v>
+        <v>-8.916257214290482</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.420578369434466</v>
+        <v>-0.4538255610633346</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.990538115431432</v>
+        <v>-9.073656094503603</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4809664055482843</v>
+        <v>-0.5142135971771524</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.350068437935434</v>
+        <v>-9.433186417007605</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6194282312518347</v>
+        <v>-0.6526754228807032</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.400417501389656</v>
+        <v>-9.483535480461827</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6316518366763462</v>
+        <v>-0.6648990283052143</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776674</v>
+        <v>3.500446096776671</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.498036778811052</v>
+        <v>-9.581154757883223</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6676577970231357</v>
+        <v>-0.7009049886520038</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.494345853854641</v>
+        <v>-9.577463832926812</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6661814270405713</v>
+        <v>-0.6994286186694398</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.698604029184505</v>
+        <v>-9.781722008256676</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7423715000538746</v>
+        <v>-0.7756186916827428</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.916641800815682</v>
+        <v>-9.999759779887853</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8251040542219097</v>
+        <v>-0.8583512458507778</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.165457029933451</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.843171969148234</v>
+        <v>-9.926289948220404</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7803444200615086</v>
+        <v>-0.8135916116903772</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.091987198266002</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.01829638653478</v>
+        <v>-10.10141436560695</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.835838966268609</v>
+        <v>-0.8690861578974776</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.267111615652546</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.25274848054927</v>
+        <v>-10.33586645962144</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.936838968776001</v>
+        <v>-0.9700861604048696</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.267111615652546</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.54055232508651</v>
+        <v>-10.62367030415868</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.058632697364873</v>
+        <v>-1.091879888993741</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.554915460189784</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.59333848068683</v>
+        <v>-10.676456459759</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.078631369766447</v>
+        <v>-1.111878561395315</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.650590946772181</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.82536740042309</v>
+        <v>-10.90848537949526</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.168749209031838</v>
+        <v>-1.201996400660705</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.712603643960604</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.77335188645428</v>
+        <v>-10.85646986552645</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.143952667757911</v>
+        <v>-1.177199859386779</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.712603643960604</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.9150237281784</v>
+        <v>-10.99814170725057</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.202096631346301</v>
+        <v>-1.235343822975169</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.712603643960604</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.86543288375357</v>
+        <v>-10.94855086282574</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.167206883411495</v>
+        <v>-1.200454075040363</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.663012799535771</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.66628077651647</v>
+        <v>-10.74939875558864</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.100597174163338</v>
+        <v>-1.133844365792207</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.497690273585957</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.44043562379706</v>
+        <v>-10.52355360286923</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.000680040039366</v>
+        <v>-1.033927231668234</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.455763597998794</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.31585696745947</v>
+        <v>-10.39897494653164</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.94970943294827</v>
+        <v>-0.9829566245771386</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.455763597998794</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.36875225550375</v>
+        <v>-10.45187023457592</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9682337740038767</v>
+        <v>-1.001480965632745</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.450808251910348</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.084843524575</v>
+        <v>-10.16796150364717</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.848936577393741</v>
+        <v>-0.8821837690226095</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.450808251910348</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.01347713196536</v>
+        <v>-10.09659511103753</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8301272827437476</v>
+        <v>-0.8633744743726153</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.379441859300699</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.749640264761286</v>
+        <v>-9.832758243833457</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7344760171750271</v>
+        <v>-0.7677232088038952</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.379441859300699</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.482398463892888</v>
+        <v>-9.565516442965059</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6294138573270414</v>
+        <v>-0.6626610489559099</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.379441859300699</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781941</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.384491425216398</v>
+        <v>-9.467609404288568</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.5905513568299061</v>
+        <v>-0.6237985484587742</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.311456109440143</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567235</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.36053788424044</v>
+        <v>-9.44365586331261</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5803014342940291</v>
+        <v>-0.6135486259228977</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.287502568464185</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487766</v>
+        <v>3.789307536487764</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.096477945917643</v>
+        <v>-9.179595924989814</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4879377751266629</v>
+        <v>-0.5211849667555311</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.023442630141389</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309717</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.389398322412806</v>
+        <v>-8.472516301484976</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2078929593850285</v>
+        <v>-0.2411401510138971</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.023442630141389</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858719</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.349214024046615</v>
+        <v>-8.432332003118786</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.191475616150711</v>
+        <v>-0.2247228077795795</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.983258331775199</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.856158176096464</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.269144228508811</v>
+        <v>-8.352262207580981</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1600808767148325</v>
+        <v>-0.1933280683437006</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.903188536237395</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.035663006279211</v>
+        <v>-8.118780985351382</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.05876395898514009</v>
+        <v>-0.09201115061400866</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.669707314007796</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255782</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.885996615271696</v>
+        <v>-7.969114594343867</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.001789612895093384</v>
+        <v>-0.03503680452396152</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.57680382276526</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.75372114164081</v>
+        <v>-7.83683912071298</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.04648806330428812</v>
+        <v>0.01324087167541999</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.444528349134373</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.563121466967657</v>
+        <v>-7.646239446039828</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1255429938611861</v>
+        <v>0.09229580223231793</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.253928674461221</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.314121668284076</v>
+        <v>-7.397239647356247</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2380492545582773</v>
+        <v>0.2048020629294087</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.253928674461221</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.419711658057181</v>
+        <v>-7.502829637129351</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.06783732904981665</v>
+        <v>0.03459013742094852</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.359518664234325</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457896</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.438446560175778</v>
+        <v>-7.521564539247948</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1088877100794643</v>
+        <v>0.07564051845059616</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.359518664234325</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.290506518768178</v>
+        <v>-7.373624497840349</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.04818480395433644</v>
+        <v>0.01493761232546831</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.339197748325767</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879198</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.266277882379206</v>
+        <v>-7.349395861451376</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.04916227225644709</v>
+        <v>0.01591508062757896</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.314969111936795</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.222729475608515</v>
+        <v>-7.305847454680686</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.05962102286963011</v>
+        <v>0.02637383124076198</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.314969111936795</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.980581082154657</v>
+        <v>-7.063699061226828</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1709427346323165</v>
+        <v>0.1376955430034483</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.314969111936795</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.917351710386309</v>
+        <v>-7.000469689458479</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1907666037988509</v>
+        <v>0.1575194121699828</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.314969111936795</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.794060575569178</v>
+        <v>-6.877178554641349</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.23758115173628</v>
+        <v>0.2043339601074119</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.191677977119665</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.772911376665735</v>
+        <v>-6.856029355737905</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2537418095349828</v>
+        <v>0.2204946179061142</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.170528778216221</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.52914593468229</v>
+        <v>-6.612263913754461</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3470286946754109</v>
+        <v>0.3137815030465427</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.170528778216221</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.382248906964421</v>
+        <v>-6.465366886036591</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4079118196825751</v>
+        <v>0.3746646280537069</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.122870536237633</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749179</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.132398513015346</v>
+        <v>-6.215516492087517</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5005940522459071</v>
+        <v>0.4673468606170386</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.122870536237633</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.956506420547914</v>
+        <v>-6.039624399620084</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5745500127535288</v>
+        <v>0.5413028211246602</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.122870536237633</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.78505995752545</v>
+        <v>-5.868177936597621</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6564561040170678</v>
+        <v>0.6232089123881996</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.9514240732151701</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102774</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.560026957856627</v>
+        <v>-5.643144936928798</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7454897815008938</v>
+        <v>0.7122425898720257</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.7263910735463472</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.764614304353066</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.496391215622693</v>
+        <v>-5.579509194694864</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7756388794487847</v>
+        <v>0.7423916878199166</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.6627553313124127</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544775</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.403391174416795</v>
+        <v>-5.486509153488965</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7940331547149397</v>
+        <v>0.7607859630860716</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.6627553313124127</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712285</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.162960677611935</v>
+        <v>-5.246078656684105</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8919484300617615</v>
+        <v>0.8587012384328929</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.4223248345075524</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837675</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.09071810944074</v>
+        <v>-5.17383608851291</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9247747711650596</v>
+        <v>0.891527579536191</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.4223248345075524</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349959</v>
+        <v>3.822323422349957</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.037719787159352</v>
+        <v>-5.120837766231523</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9466526839949547</v>
+        <v>0.9134054923660861</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.3669885755056136</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972331</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.946220878224191</v>
+        <v>-5.012032880751796</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9802503187890126</v>
+        <v>0.9539255177779706</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3669885755056136</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145933</v>
+        <v>3.81866537614593</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.72620008018718</v>
+        <v>-4.792012082714785</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.069837675014431</v>
+        <v>1.043512874003389</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2257687304376333</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009945</v>
+        <v>3.843270952009942</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.593332391123902</v>
+        <v>-4.659144393651507</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.138878933441565</v>
+        <v>1.112554132430523</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2257687304376333</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.433817287604533</v>
+        <v>-4.499629290132138</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.203830819289615</v>
+        <v>1.177506018278573</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.06625362691826342</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.289145142504795</v>
+        <v>-4.3549571450324</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.27178777989095</v>
+        <v>1.245462978879908</v>
       </c>
       <c r="F1932" t="n">
         <v>0.078418518181474</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.349019969862487</v>
+        <v>-4.414831972390092</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.233875340349299</v>
+        <v>1.207550539338257</v>
       </c>
       <c r="F1933" t="n">
         <v>0.01854369082378188</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.262220472083479</v>
+        <v>-4.328032474611083</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290995632783468</v>
+        <v>1.264670831772427</v>
       </c>
       <c r="F1934" t="n">
         <v>0.01854369082378188</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.264690178545285</v>
+        <v>-4.330502181072889</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.290080151572158</v>
+        <v>1.263755350561116</v>
       </c>
       <c r="F1935" t="n">
         <v>0.01607398436197571</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.333060364869295</v>
+        <v>-4.398872367396899</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.273738999517256</v>
+        <v>1.247414198506214</v>
       </c>
       <c r="F1936" t="n">
         <v>0.02534968339819066</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.441598545785429</v>
+        <v>-4.507410548313033</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.220760435782694</v>
+        <v>1.194435634771652</v>
       </c>
       <c r="F1937" t="n">
         <v>0.02534968339819066</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.472591705114135</v>
+        <v>-4.538403707641739</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.033072737091598</v>
+        <v>1.006747936080557</v>
       </c>
       <c r="F1938" t="n">
         <v>0.02534968339819066</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675893</v>
+        <v>3.746038950675891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.297117445321666</v>
+        <v>-4.36292944784927</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.107829673000374</v>
+        <v>1.081504871989332</v>
       </c>
       <c r="F1939" t="n">
         <v>0.02534968339819066</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695436</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.333217032905962</v>
+        <v>-4.473865700490519</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.069131866727862</v>
+        <v>1.012872399694039</v>
       </c>
       <c r="F1940" t="n">
         <v>0.02534968339819066</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.536243610449195</v>
+        <v>-4.676892278033752</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9910526209304746</v>
+        <v>0.9347931538966519</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1776768941450427</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.378318011513902</v>
+        <v>-4.518966679098459</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.064395246936724</v>
+        <v>1.008135779902901</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1776768941450427</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.292074548487524</v>
+        <v>-4.432723216072081</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.093838902721135</v>
+        <v>1.037579435687313</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1776768941450427</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.293257633138586</v>
+        <v>-4.433906300723143</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.085141444305237</v>
+        <v>1.028881977271414</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1833199426115543</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.170129926144503</v>
+        <v>-4.31077859372906</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.134944400135971</v>
+        <v>1.078684933102148</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1833199426115543</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.077319444693643</v>
+        <v>-4.2179681122782</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.101341284607681</v>
+        <v>1.045081817573858</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.09050946116069492</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.028756392472613</v>
+        <v>-4.16940506005717</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.122639981420694</v>
+        <v>1.066380514386871</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.04194640893966473</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.916085174236363</v>
+        <v>-4.05673384182092</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.162784177226917</v>
+        <v>1.106524710193094</v>
       </c>
       <c r="F1948" t="n">
         <v>0.07072480929658548</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.80370817305369</v>
+        <v>-3.944356840638247</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.213226273530653</v>
+        <v>1.15696680649683</v>
       </c>
       <c r="F1949" t="n">
         <v>0.07072480929658548</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.001942741940421</v>
+        <v>-4.142591409524978</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.1454296477445</v>
+        <v>1.089170180710677</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1275097595901451</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306604617532</v>
+        <v>3.643066046175318</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.0849440229657</v>
+        <v>-4.225592690550257</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9505848553350416</v>
+        <v>0.8943253883012188</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1460806441173189</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199265</v>
+        <v>3.682712735199263</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.212011029272688</v>
+        <v>-4.352659696857245</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.019907713531452</v>
+        <v>0.963648246497629</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1460806441173189</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660763</v>
+        <v>3.733008865660762</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.298609612253791</v>
+        <v>-4.439258279838348</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9997813064413337</v>
+        <v>0.9435218394075109</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1460806441173189</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383419</v>
+        <v>3.741170494383417</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.26022594969564</v>
+        <v>-4.400874617280197</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.012554212806963</v>
+        <v>0.9562947457731401</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1076969815591677</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114362200248</v>
+        <v>3.751143622002478</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.083109619660473</v>
+        <v>-4.223758287245031</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.080129773666331</v>
+        <v>1.023870306632508</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1076969815591677</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263896</v>
+        <v>3.741324873263895</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.05340749568418</v>
+        <v>-4.194056163268737</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.092694015018762</v>
+        <v>1.036434547984939</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1121671067744811</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481229</v>
+        <v>3.750725801481227</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.874032074445412</v>
+        <v>-4.014680742029969</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.158231158820683</v>
+        <v>1.10197169178686</v>
       </c>
       <c r="F1957" t="n">
         <v>0.04460965139623763</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452225</v>
+        <v>3.716988143452223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.919046287966018</v>
+        <v>-4.059694955550576</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.121032928744031</v>
+        <v>1.064773461710208</v>
       </c>
       <c r="F1958" t="n">
         <v>0.01426075608163302</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979532</v>
+        <v>3.737023032979529</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.186050798238454</v>
+        <v>-4.326699465823011</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.019922686974002</v>
+        <v>0.9636632199401793</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1801022819613156</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.474838018697369</v>
+        <v>-4.615486686281926</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9036117206869374</v>
+        <v>0.8473522536531146</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2811884020603159</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.70556808628545</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.442362432526597</v>
+        <v>-4.583011100111154</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.914201916709563</v>
+        <v>0.8579424496757402</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2811884020603159</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.4233243048193</v>
+        <v>-4.563972972403857</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9183418870007269</v>
+        <v>0.8620824199669039</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3393720133915105</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.454450935969918</v>
+        <v>-4.595099603554475</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.08347310347916</v>
+        <v>1.027213636445337</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3393720133915105</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.50677131657071</v>
+        <v>-4.647419984155267</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.063378280224977</v>
+        <v>1.007118813191154</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3044251533826383</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259119</v>
+        <v>3.787422005259117</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.651094222495629</v>
+        <v>-4.791742890080186</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.011657648251935</v>
+        <v>0.9553981812181125</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3044251533826383</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989904</v>
+        <v>3.781497674989902</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.503351252260626</v>
+        <v>-4.643999919845183</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.149907484137958</v>
+        <v>1.093648017104135</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1366177961477552</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651166</v>
+        <v>3.802242353651163</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.605365934791847</v>
+        <v>-4.746014602376404</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.111895232656951</v>
+        <v>1.055635765623128</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1366177961477552</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864725</v>
+        <v>3.805605409864722</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.468756590697755</v>
+        <v>-4.771436046287859</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.167201318686246</v>
+        <v>1.046129536450204</v>
       </c>
       <c r="F1968" t="n">
-        <v>-8.452053662677539e-06</v>
+        <v>-0.1620392400592104</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.955055308046898</v>
+        <v>2.857836835243569</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360612</v>
+        <v>3.798236219360609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.611521923520405</v>
+        <v>-4.914201379110509</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.109175662297296</v>
+        <v>0.9881038800612545</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1427737848763131</v>
+        <v>-0.3048045728818608</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.868476585093418</v>
+        <v>2.771258112290089</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268422</v>
+        <v>3.86735906126842</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.549223924744282</v>
+        <v>-4.851903380334387</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.200430415604566</v>
+        <v>1.079358633368524</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1427737848763131</v>
+        <v>-0.3048045728818608</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.934812138890239</v>
+        <v>2.83759366608691</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462185</v>
+        <v>3.848725564462184</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.347433727079125</v>
+        <v>-4.650113182669229</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9897273670600273</v>
+        <v>0.8686555848239854</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.0552444072928413</v>
+        <v>-0.1067863807127064</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.76220392658113</v>
+        <v>2.664985453777801</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322409</v>
+        <v>3.841441242322406</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.287543045436531</v>
+        <v>-4.590222501026636</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.08397387203924</v>
+        <v>0.9629020898031979</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1151350889354348</v>
+        <v>-0.04689569907011293</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.868428567888861</v>
+        <v>2.771210095085532</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.806563277902788</v>
+        <v>3.722599359965806</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.746637071339096</v>
+        <v>2.702909545675169</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.287543045436531</v>
+        <v>-4.590222501026636</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.08397387203924</v>
+        <v>0.9629020898031979</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1151350889354348</v>
+        <v>-0.04689569907011293</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.739700868325464</v>
+        <v>2.695973342661537</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-37.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.3%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-620.6%</t>
+          <t>-614.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.9%</t>
+          <t>-277.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-257.9%</t>
+          <t>-138.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-228.7%</t>
+          <t>-231.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.4%</t>
+          <t>-172.2%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.533255825547851</v>
+        <v>-8.45013784647568</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3005229042446977</v>
+        <v>-0.2672757126158296</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.916257214290482</v>
+        <v>-8.833139235218312</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4538255610633346</v>
+        <v>-0.420578369434466</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.073656094503603</v>
+        <v>-9.042524245531759</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5142135971771524</v>
+        <v>-0.5017608575884149</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.76706510644827</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.08655787912927</v>
+        <v>2.055366201069075</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.433186417007605</v>
+        <v>-9.40205456803576</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6526754228807032</v>
+        <v>-0.6402226832919653</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.76706510644827</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.09190818242732</v>
+        <v>2.060716504367124</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.483535480461827</v>
+        <v>-9.452403631489982</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6648990283052143</v>
+        <v>-0.6524462887164768</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.765428039802166</v>
+        <v>-1.817414169902492</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.069614764311964</v>
+        <v>2.038423086251769</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776671</v>
+        <v>3.500446096776673</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.581154757883223</v>
+        <v>-9.550022908911378</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7009049886520038</v>
+        <v>-0.6884522490632663</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.915033447323889</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.014084948480895</v>
+        <v>1.9828932704207</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.577463832926812</v>
+        <v>-9.546331983954968</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6994286186694398</v>
+        <v>-0.6869758790807019</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.915033447323889</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.014084948480895</v>
+        <v>1.9828932704207</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.781722008256676</v>
+        <v>-9.750590159284831</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7756186916827428</v>
+        <v>-0.7631659520940053</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.990686261837552</v>
+        <v>-2.042672391937877</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.943014778831144</v>
+        <v>1.911823100770949</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.999759779887853</v>
+        <v>-9.968627930916009</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8583512458507778</v>
+        <v>-0.8458985062620399</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.165457029933451</v>
+        <v>-2.217443160033776</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.842634872458041</v>
+        <v>1.811443194397845</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.926289948220404</v>
+        <v>-9.89515809924856</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8135916116903772</v>
+        <v>-0.8011388721016393</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.091987198266002</v>
+        <v>-2.143973328366328</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.902088472951931</v>
+        <v>1.870896794891736</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.10141436560695</v>
+        <v>-10.0702825166351</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8690861578974776</v>
+        <v>-0.8566334183087401</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.319097745752872</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.811569043267521</v>
+        <v>1.780377365207326</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.33586645962144</v>
+        <v>-10.30473461064959</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9700861604048696</v>
+        <v>-0.9576334208161321</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.319097745752872</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.804349878365925</v>
+        <v>1.77315820030573</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.62367030415868</v>
+        <v>-10.59253845518683</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.091879888993741</v>
+        <v>-1.079427149405003</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.554915460189784</v>
+        <v>-2.60690159029011</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.624995380869606</v>
+        <v>1.593803702809411</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.676456459759</v>
+        <v>-10.64532461078716</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.111878561395315</v>
+        <v>-1.099425821806578</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.650590946772181</v>
+        <v>-2.702577076872507</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.568705878758724</v>
+        <v>1.537514200698529</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.90848537949526</v>
+        <v>-10.87735353052342</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.201996400660705</v>
+        <v>-1.189543661071968</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.76458977406093</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.534191989074785</v>
+        <v>1.50300031101459</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.85646986552645</v>
+        <v>-10.82533801655461</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.177199859386779</v>
+        <v>-1.164747119798042</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.76458977406093</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.538182324761186</v>
+        <v>1.506990646700991</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.99814170725057</v>
+        <v>-10.96700985827873</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.235343822975169</v>
+        <v>-1.222891083386432</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.76458977406093</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.536707097862444</v>
+        <v>1.505515419802249</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.94855086282574</v>
+        <v>-10.91741901385389</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.200454075040363</v>
+        <v>-1.188001335451626</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.663012799535771</v>
+        <v>-2.714998929636096</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.581515014682217</v>
+        <v>1.550323336622022</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.74939875558864</v>
+        <v>-10.71826690661679</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.133844365792207</v>
+        <v>-1.121391626203469</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.497690273585957</v>
+        <v>-2.549676403686283</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.667657396605422</v>
+        <v>1.636465718545226</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.52355360286923</v>
+        <v>-10.49242175389738</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.033927231668234</v>
+        <v>-1.021474492079495</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.507749728099119</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.702392474993929</v>
+        <v>1.671200796933733</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.39897494653164</v>
+        <v>-10.36784309755979</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9829566245771386</v>
+        <v>-0.9705038849884002</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.507749728099119</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.703531619549988</v>
+        <v>1.672339941489792</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.45187023457592</v>
+        <v>-10.42073838560408</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.001480965632745</v>
+        <v>-0.9890282260440069</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.502794382010673</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.709138601365163</v>
+        <v>1.677946923304968</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.16796150364717</v>
+        <v>-10.13682965467533</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8821837690226095</v>
+        <v>-0.8697310294338712</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.502794382010673</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.7148723056038</v>
+        <v>1.683680627543604</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.09659511103753</v>
+        <v>-10.06546326206568</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8633744743726153</v>
+        <v>-0.8509217347838769</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.431427989401025</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.716763200715528</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.832758243833457</v>
+        <v>-9.801626394861611</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7677232088038952</v>
+        <v>-0.7552704692151568</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.431427989401025</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.70687971940262</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.565516442965059</v>
+        <v>-9.534384593993213</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6626610489559099</v>
+        <v>-0.6502083093671716</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.431427989401025</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.705045158903246</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781941</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.467609404288568</v>
+        <v>-9.436477555316722</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6237985484587742</v>
+        <v>-0.6113458088700359</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.363442239540468</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.74553629384612</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567235</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.44365586331261</v>
+        <v>-9.412524014340764</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6135486259228977</v>
+        <v>-0.6010958863341593</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.339488698564511</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.760576924577188</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487764</v>
+        <v>3.789307536487765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.179595924989814</v>
+        <v>-9.148464076017968</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5211849667555311</v>
+        <v>-0.5087322271667927</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.075428760241715</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.905752571409113</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309717</v>
+        <v>3.833249172309719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.472516301484976</v>
+        <v>-8.44138445251313</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2411401510138971</v>
+        <v>-0.2286874114251587</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.075428760241715</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.902965537748812</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858719</v>
+        <v>3.839370871858722</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.432332003118786</v>
+        <v>-8.40120015414694</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2247228077795795</v>
+        <v>-0.2122700681908412</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-2.035244461875524</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>1.927419740656368</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096464</v>
+        <v>3.856158176096467</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.352262207580981</v>
+        <v>-8.321130358609135</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1933280683437006</v>
+        <v>-0.1808753287549623</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-1.95517466633772</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>1.974828439199808</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.118780985351382</v>
+        <v>-8.087649136379536</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.09201115061400866</v>
+        <v>-0.07955841102527028</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.721693444108122</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.122841601375419</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255782</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.969114594343867</v>
+        <v>-7.937982745372021</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03503680452396152</v>
+        <v>-0.02258406493522314</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.628789952865586</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.175691485807981</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.83683912071298</v>
+        <v>-7.805707271741134</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.01324087167541999</v>
+        <v>0.02569361126415837</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.496514479234699</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.25042425673354</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.646239446039828</v>
+        <v>-7.615107597067982</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.09229580223231793</v>
+        <v>0.1047485418210563</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.305914804561546</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.367599122225069</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.397239647356247</v>
+        <v>-7.366107798384401</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2048020629294087</v>
+        <v>0.2172548025181471</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.305914804561546</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.380505463448728</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.502829637129351</v>
+        <v>-7.471697788157505</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03459013742094852</v>
+        <v>0.0470428770096869</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.41150479433465</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.189175539985647</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.521564539247948</v>
+        <v>-7.490432690276102</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.07564051845059616</v>
+        <v>0.08809325803933454</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.41150479433465</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.237719881862733</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.373624497840349</v>
+        <v>-7.342492648868503</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.01493761232546831</v>
+        <v>0.02739035191420669</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.391183878426093</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.1300335087197</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.349395861451376</v>
+        <v>-7.31826401247953</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01591508062757896</v>
+        <v>0.02836782021631734</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.36695524203712</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.135856704299605</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.305847454680686</v>
+        <v>-7.27471560570884</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02637383124076198</v>
+        <v>0.03882657082950036</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.36695524203712</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.128896092204512</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.063699061226828</v>
+        <v>-7.032567212254982</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1376955430034483</v>
+        <v>0.1501482825921867</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.36695524203712</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.143358446585655</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.000469689458479</v>
+        <v>-6.969337840486634</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1575194121699828</v>
+        <v>0.1699721517587212</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.36695524203712</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.13789056704485</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.877178554641349</v>
+        <v>-6.846046705669503</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2043339601074119</v>
+        <v>0.2167866996961503</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.24366410721999</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.209363341945705</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.856029355737905</v>
+        <v>-6.824897506766059</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2204946179061142</v>
+        <v>0.2329473574948526</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.222514908316547</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.229753839525096</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.612263913754461</v>
+        <v>-6.581132064782615</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3137815030465427</v>
+        <v>0.3262342426352811</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.222514908316547</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.225534547872147</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.465366886036591</v>
+        <v>-6.434235037064745</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3746646280537069</v>
+        <v>0.3871173676424453</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.174856666337959</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.256253806979315</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749179</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.215516492087517</v>
+        <v>-6.184384643115671</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4673468606170386</v>
+        <v>0.4797996002057769</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.174856666337959</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.248995881963018</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.039624399620084</v>
+        <v>-6.008492550648239</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5413028211246602</v>
+        <v>0.5537555607133986</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.174856666337959</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.252595005483666</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.868177936597621</v>
+        <v>-5.837046087625775</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6232089123881996</v>
+        <v>0.635661651976938</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-1.003410203315496</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.368790389351698</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102774</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.643144936928798</v>
+        <v>-5.612013087956952</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7122425898720257</v>
+        <v>0.7246953294607641</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.7783772036466728</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.502830666769289</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353066</v>
+        <v>3.764614304353068</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.579509194694864</v>
+        <v>-5.548377345723018</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7423916878199166</v>
+        <v>0.754844427408655</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.7147414614127383</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.545706913163967</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544775</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.486509153488965</v>
+        <v>-5.455377304517119</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7607859630860716</v>
+        <v>0.77323870267481</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.7147414614127383</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.526901171947762</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712285</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.246078656684105</v>
+        <v>-5.214946807712259</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8587012384328929</v>
+        <v>0.8711539780216313</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.474310964607878</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.672902546655556</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837675</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.17383608851291</v>
+        <v>-5.142704239541064</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.891527579536191</v>
+        <v>0.9039803191249294</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.474310964607878</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.676831860490376</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349957</v>
+        <v>3.822323422349958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.120837766231523</v>
+        <v>-5.089705917259677</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9134054923660861</v>
+        <v>0.9258582319548245</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3669885755056136</v>
+        <v>-0.4189747056059392</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.741903877869075</v>
+        <v>2.71071219980888</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972331</v>
+        <v>3.848613050972332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.012032880751796</v>
+        <v>-4.98090103177995</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9539255177779706</v>
+        <v>0.966378257366709</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3669885755056136</v>
+        <v>-0.4189747056059392</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.738901949089068</v>
+        <v>2.707710271028873</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614593</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.792012082714785</v>
+        <v>-4.897150497936862</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.043512874003389</v>
+        <v>1.001457507914558</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2257687304376333</v>
+        <v>-0.4179286467277993</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.825212893140471</v>
+        <v>2.709916943366371</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009942</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.659144393651507</v>
+        <v>-4.764282808873585</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.112554132430523</v>
+        <v>1.070498766341692</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2257687304376333</v>
+        <v>-0.4179286467277993</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.841107075942294</v>
+        <v>2.725811126168194</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.499629290132138</v>
+        <v>-4.604767705354215</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.177506018278573</v>
+        <v>1.135450652189742</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06625362691826342</v>
+        <v>-0.2584135432084294</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.937961982494218</v>
+        <v>2.822666032720118</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.3549571450324</v>
+        <v>-4.460095560254477</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.245462978879908</v>
+        <v>1.203407612791077</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.078418518181474</v>
+        <v>-0.1137413981086919</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.0348533721155</v>
+        <v>2.9195574223414</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.414831972390092</v>
+        <v>-4.51997038761217</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.207550539338257</v>
+        <v>1.165495173249426</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.01854369082378188</v>
+        <v>-0.1736162254663841</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.984965967102311</v>
+        <v>2.869670017328211</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.328032474611083</v>
+        <v>-4.433170889833161</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.264670831772427</v>
+        <v>1.222615465683596</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.01854369082378188</v>
+        <v>-0.1736162254663841</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.007366460424877</v>
+        <v>2.892070510650777</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.330502181072889</v>
+        <v>-4.435640596294967</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.263755350561116</v>
+        <v>1.221699984472286</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.01607398436197571</v>
+        <v>-0.1760859319281902</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.005957037921205</v>
+        <v>2.890661088147106</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.398872367396899</v>
+        <v>-4.504010782618977</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.247414198506214</v>
+        <v>1.205358832417383</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.1668102328919753</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.022529379817636</v>
+        <v>2.907233430043537</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.507410548313033</v>
+        <v>-4.612548963535111</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.194435634771652</v>
+        <v>1.152380268682821</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.1668102328919753</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.012966088449527</v>
+        <v>2.897670138675428</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.538403707641739</v>
+        <v>-4.643542122863816</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.006747936080557</v>
+        <v>0.9646925699917257</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.1668102328919753</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.837675653489914</v>
+        <v>2.722379703715815</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.746038950675893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.36292944784927</v>
+        <v>-4.468067863071347</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.081504871989332</v>
+        <v>1.039449505900501</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.1668102328919753</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.842242885481702</v>
+        <v>2.726946935707602</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695436</v>
+        <v>3.765020747695439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.473865700490519</v>
+        <v>-4.579004115712596</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.012872399694039</v>
+        <v>0.9708170336052087</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.1668102328919753</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.817984914242909</v>
+        <v>2.702688964468809</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.676892278033752</v>
+        <v>-4.782030693255829</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9347931538966519</v>
+        <v>0.8927377878078209</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1776768941450427</v>
+        <v>-0.3698368104352087</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.699300352936874</v>
+        <v>2.584004403162775</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.518966679098459</v>
+        <v>-4.624105094320536</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.008135779902901</v>
+        <v>0.9660804138140704</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1776768941450427</v>
+        <v>-0.3698368104352087</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.709472739369007</v>
+        <v>2.594176789594907</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.432723216072081</v>
+        <v>-4.537861631294159</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.037579435687313</v>
+        <v>0.9955240695984817</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1776768941450427</v>
+        <v>-0.3698368104352087</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.704419009942867</v>
+        <v>2.589123060168768</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.433906300723143</v>
+        <v>-4.53904471594522</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.028881977271414</v>
+        <v>0.9868266111825827</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1833199426115543</v>
+        <v>-0.3754798589017202</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.692808956307486</v>
+        <v>2.577513006533386</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.31077859372906</v>
+        <v>-4.415917008951137</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.078684933102148</v>
+        <v>1.036629567013318</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1833199426115543</v>
+        <v>-0.3754798589017202</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.693360829340588</v>
+        <v>2.578064879566488</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.2179681122782</v>
+        <v>-4.323106527500277</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.045081817573858</v>
+        <v>1.003026451485027</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.09050946116069492</v>
+        <v>-0.2826693774508608</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.678319810102469</v>
+        <v>2.563023860328369</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.16940506005717</v>
+        <v>-4.274543475279247</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.066380514386871</v>
+        <v>1.02432514829804</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.04194640893966473</v>
+        <v>-0.2341063252298307</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.709331117359687</v>
+        <v>2.594035167585588</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.05673384182092</v>
+        <v>-4.161872257042997</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.106524710193094</v>
+        <v>1.064469344104263</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07072480929658548</v>
+        <v>-0.1214351069935805</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.772009556813161</v>
+        <v>2.656713607039061</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.944356840638247</v>
+        <v>-4.049495255860324</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.15696680649683</v>
+        <v>1.114911440407999</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07072480929658548</v>
+        <v>-0.1214351069935805</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.777500852643828</v>
+        <v>2.662204902869728</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.142591409524978</v>
+        <v>-4.247729824747055</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.089170180710677</v>
+        <v>1.047114814621846</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1275097595901451</v>
+        <v>-0.319669675880311</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.670057313080329</v>
+        <v>2.554761363306229</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175318</v>
+        <v>3.64306604617532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.225592690550257</v>
+        <v>-4.330731105772334</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8943253883012188</v>
+        <v>0.8522700222123878</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1460806441173189</v>
+        <v>-0.3382405604074848</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.497270502364678</v>
+        <v>2.381974552590578</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199263</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.352659696857245</v>
+        <v>-4.457798112079322</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.963648246497629</v>
+        <v>0.9215928804087983</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1460806441173189</v>
+        <v>-0.3382405604074848</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.617420163083883</v>
+        <v>2.502124213309784</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660762</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.439258279838348</v>
+        <v>-4.544396695060425</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9435218394075109</v>
+        <v>0.9014664733186799</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1460806441173189</v>
+        <v>-0.3382405604074848</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.631933189186206</v>
+        <v>2.516637239412107</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383417</v>
+        <v>3.741170494383419</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.400874617280197</v>
+        <v>-4.506013032502274</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9562947457731401</v>
+        <v>0.9142393796843091</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1076969815591677</v>
+        <v>-0.2998568978493336</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.652382828063466</v>
+        <v>2.537086878289366</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002478</v>
+        <v>3.75114362200248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.223758287245031</v>
+        <v>-4.328896702467108</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.023870306632508</v>
+        <v>0.9818149405436776</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1076969815591677</v>
+        <v>-0.2998568978493336</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.649111856908767</v>
+        <v>2.533815907134668</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263895</v>
+        <v>3.741324873263896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.194056163268737</v>
+        <v>-4.299194578490814</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.036434547984939</v>
+        <v>0.9943791818961081</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1121671067744811</v>
+        <v>-0.304327023064647</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.647113173541493</v>
+        <v>2.531817223767393</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481227</v>
+        <v>3.750725801481229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.014680742029969</v>
+        <v>-4.119819157252047</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.10197169178686</v>
+        <v>1.05991632569803</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04460965139623763</v>
+        <v>-0.1475502648939283</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.734966203750338</v>
+        <v>2.619670253976239</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452223</v>
+        <v>3.716988143452224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.059694955550576</v>
+        <v>-4.164833370772653</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.064773461710208</v>
+        <v>1.022718095621377</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01426075608163302</v>
+        <v>-0.1778991602085329</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.697564321893165</v>
+        <v>2.582268372119066</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.737023032979531</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.326699465823011</v>
+        <v>-4.431837881045088</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9636632199401793</v>
+        <v>0.9216078538513484</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1801022819613156</v>
+        <v>-0.3722621982514815</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.586638061406342</v>
+        <v>2.471342111632242</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.615486686281926</v>
+        <v>-4.720625101504003</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8473522536531146</v>
+        <v>0.8052968875642836</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2811884020603159</v>
+        <v>-0.4733483183504819</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.525190311243443</v>
+        <v>2.409894361469344</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.583011100111154</v>
+        <v>-4.688149515333231</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8579424496757402</v>
+        <v>0.8158870835869092</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2811884020603159</v>
+        <v>-0.4733483183504819</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.52279027279776</v>
+        <v>2.40749432302366</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.563972972403857</v>
+        <v>-4.669111387625934</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8620824199669039</v>
+        <v>0.8200270538780732</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3393720133915105</v>
+        <v>-0.5315319296816764</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.484404825207288</v>
+        <v>2.369108875433188</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.595099603554475</v>
+        <v>-4.700238018776552</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.027213636445337</v>
+        <v>0.9851582703565063</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3393720133915105</v>
+        <v>-0.5315319296816764</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.661986694145968</v>
+        <v>2.546690744371869</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537861</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.647419984155267</v>
+        <v>-4.752558399377344</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.007118813191154</v>
+        <v>0.9650634471023232</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3044251533826383</v>
+        <v>-0.4965850696728042</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.683788139137425</v>
+        <v>2.568492189363326</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259117</v>
+        <v>3.787422005259119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.791742890080186</v>
+        <v>-4.896881305302263</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9553981812181125</v>
+        <v>0.9133428151292815</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3044251533826383</v>
+        <v>-0.4965850696728042</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.689796669534351</v>
+        <v>2.574500719760252</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989902</v>
+        <v>3.781497674989904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.643999919845183</v>
+        <v>-4.74913833506726</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.093648017104135</v>
+        <v>1.051592651015304</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1366177961477552</v>
+        <v>-0.3287777124379211</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.869633731667303</v>
+        <v>2.754337781893204</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651163</v>
+        <v>3.802242353651165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.746014602376404</v>
+        <v>-4.851153017598482</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.055635765623128</v>
+        <v>1.013580399534297</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1366177961477552</v>
+        <v>-0.3287777124379211</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.872427353198784</v>
+        <v>2.757131403424685</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864722</v>
+        <v>3.805605409864724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.771436046287859</v>
+        <v>-4.714543673504389</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.046129536450204</v>
+        <v>1.068886485563592</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1620392400592104</v>
+        <v>-0.1921683683438286</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.857836835243569</v>
+        <v>2.839759358272798</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360609</v>
+        <v>3.798236219360612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.914201379110509</v>
+        <v>-4.857309006327039</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9881038800612545</v>
+        <v>1.010860829174643</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3048045728818608</v>
+        <v>-0.334933701166479</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.771258112290089</v>
+        <v>2.753180635319318</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86735906126842</v>
+        <v>3.867359061268422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.851903380334387</v>
+        <v>-4.795011007550917</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.079358633368524</v>
+        <v>1.102115582481912</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3048045728818608</v>
+        <v>-0.334933701166479</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.83759366608691</v>
+        <v>2.819516189116139</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462184</v>
+        <v>3.848725564462185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.650113182669229</v>
+        <v>-4.593220809885759</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8686555848239854</v>
+        <v>0.8914125339373735</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1067863807127064</v>
+        <v>-0.1369155089973246</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.664985453777801</v>
+        <v>2.64690797680703</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322406</v>
+        <v>3.841441242322409</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.590222501026636</v>
+        <v>-4.533330128243166</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9629020898031979</v>
+        <v>0.985659038916586</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.04689569907011293</v>
+        <v>-0.07702482735473115</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.771210095085532</v>
+        <v>2.753132618114762</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.722599359965806</v>
+        <v>3.776562762395375</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.702909545675169</v>
+        <v>2.745404374078463</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.590222501026636</v>
+        <v>-4.533330128243166</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9629020898031979</v>
+        <v>0.985659038916586</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.04689569907011293</v>
+        <v>-0.07702482735473115</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.695973342661537</v>
+        <v>2.738468171064831</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-15.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>126.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-71.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>449.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.9%</t>
+          <t>-569.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-277.7%</t>
+          <t>-259.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-138.7%</t>
+          <t>-247.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.7%</t>
+          <t>-201.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-172.2%</t>
+          <t>-150.2%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.042524245531759</v>
+        <v>-8.990538115431432</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5017608575884149</v>
+        <v>-0.4809664055482843</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.76706510644827</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.055366201069075</v>
+        <v>2.08655787912927</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.40205456803576</v>
+        <v>-9.350068437935434</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6402226832919653</v>
+        <v>-0.6194282312518347</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.76706510644827</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.060716504367124</v>
+        <v>2.09190818242732</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.452403631489982</v>
+        <v>-9.400417501389656</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6524462887164768</v>
+        <v>-0.6316518366763462</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.817414169902492</v>
+        <v>-1.765428039802166</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.038423086251769</v>
+        <v>2.069614764311964</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.550022908911378</v>
+        <v>-9.498036778811052</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6884522490632663</v>
+        <v>-0.6676577970231357</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.915033447323889</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.9828932704207</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.546331983954968</v>
+        <v>-9.494345853854641</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6869758790807019</v>
+        <v>-0.6661814270405713</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.915033447323889</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.9828932704207</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.750590159284831</v>
+        <v>-9.698604029184505</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7631659520940053</v>
+        <v>-0.7423715000538746</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.042672391937877</v>
+        <v>-1.990686261837552</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.911823100770949</v>
+        <v>1.943014778831144</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.968627930916009</v>
+        <v>-9.916641800815682</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8458985062620399</v>
+        <v>-0.8251040542219097</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.217443160033776</v>
+        <v>-2.165457029933451</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.811443194397845</v>
+        <v>1.842634872458041</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.89515809924856</v>
+        <v>-9.843171969148234</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8011388721016393</v>
+        <v>-0.7803444200615086</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.143973328366328</v>
+        <v>-2.091987198266002</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.870896794891736</v>
+        <v>1.902088472951931</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.0702825166351</v>
+        <v>-10.01829638653478</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8566334183087401</v>
+        <v>-0.835838966268609</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.319097745752872</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.780377365207326</v>
+        <v>1.811569043267521</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.30473461064959</v>
+        <v>-10.25274848054927</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9576334208161321</v>
+        <v>-0.936838968776001</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.319097745752872</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.77315820030573</v>
+        <v>1.804349878365925</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.59253845518683</v>
+        <v>-10.54055232508651</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.079427149405003</v>
+        <v>-1.058632697364873</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.60690159029011</v>
+        <v>-2.554915460189784</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.593803702809411</v>
+        <v>1.624995380869606</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.64532461078716</v>
+        <v>-10.59333848068683</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.099425821806578</v>
+        <v>-1.078631369766447</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.702577076872507</v>
+        <v>-2.650590946772181</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.537514200698529</v>
+        <v>1.568705878758724</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.87735353052342</v>
+        <v>-10.82536740042309</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.189543661071968</v>
+        <v>-1.168749209031838</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.76458977406093</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.50300031101459</v>
+        <v>1.534191989074785</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.82533801655461</v>
+        <v>-10.77335188645428</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.164747119798042</v>
+        <v>-1.143952667757911</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.76458977406093</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.506990646700991</v>
+        <v>1.538182324761186</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.96700985827873</v>
+        <v>-10.9150237281784</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.222891083386432</v>
+        <v>-1.202096631346301</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.76458977406093</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.505515419802249</v>
+        <v>1.536707097862444</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.91741901385389</v>
+        <v>-10.86543288375357</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.188001335451626</v>
+        <v>-1.167206883411495</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.714998929636096</v>
+        <v>-2.663012799535771</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.550323336622022</v>
+        <v>1.581515014682217</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71826690661679</v>
+        <v>-10.66628077651647</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.121391626203469</v>
+        <v>-1.100597174163338</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.549676403686283</v>
+        <v>-2.497690273585957</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.636465718545226</v>
+        <v>1.667657396605422</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.49242175389738</v>
+        <v>-10.44043562379706</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.021474492079495</v>
+        <v>-1.000680040039366</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.507749728099119</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.671200796933733</v>
+        <v>1.702392474993929</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36784309755979</v>
+        <v>-10.31585696745947</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9705038849884002</v>
+        <v>-0.94970943294827</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.507749728099119</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.672339941489792</v>
+        <v>1.703531619549988</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.42073838560408</v>
+        <v>-10.36875225550375</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9890282260440069</v>
+        <v>-0.9682337740038767</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.502794382010673</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.677946923304968</v>
+        <v>1.709138601365163</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.13682965467533</v>
+        <v>-10.084843524575</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8697310294338712</v>
+        <v>-0.848936577393741</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.502794382010673</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.683680627543604</v>
+        <v>1.7148723056038</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.06546326206568</v>
+        <v>-10.01347713196536</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8509217347838769</v>
+        <v>-0.8301272827437476</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.431427989401025</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.716763200715528</v>
+        <v>1.747954878775723</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.801626394861611</v>
+        <v>-9.749640264761286</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7552704692151568</v>
+        <v>-0.7344760171750271</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.431427989401025</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.70687971940262</v>
+        <v>1.738071397462815</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.534384593993213</v>
+        <v>-9.482398463892888</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6502083093671716</v>
+        <v>-0.6294138573270414</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.431427989401025</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.705045158903246</v>
+        <v>1.736236836963442</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.436477555316722</v>
+        <v>-9.384491425216398</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6113458088700359</v>
+        <v>-0.5905513568299061</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.363442239540468</v>
+        <v>-2.311456109440143</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.74553629384612</v>
+        <v>1.776727971906315</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.412524014340764</v>
+        <v>-9.36053788424044</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6010958863341593</v>
+        <v>-0.5803014342940291</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.339488698564511</v>
+        <v>-2.287502568464185</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.760576924577188</v>
+        <v>1.791768602637383</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.148464076017968</v>
+        <v>-9.096477945917643</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5087322271667927</v>
+        <v>-0.4879377751266629</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.075428760241715</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.905752571409113</v>
+        <v>1.936944249469309</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.44138445251313</v>
+        <v>-8.389398322412806</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2286874114251587</v>
+        <v>-0.2078929593850285</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.075428760241715</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.902965537748812</v>
+        <v>1.934157215809008</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858722</v>
+        <v>3.839370871858721</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.40120015414694</v>
+        <v>-8.349214024046615</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2122700681908412</v>
+        <v>-0.191475616150711</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.035244461875524</v>
+        <v>-1.983258331775199</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.927419740656368</v>
+        <v>1.958611418716564</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096467</v>
+        <v>3.856158176096466</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.321130358609135</v>
+        <v>-8.205772241020389</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1808753287549623</v>
+        <v>-0.1347320817194637</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.95517466633772</v>
+        <v>-1.839816548748972</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.974828439199808</v>
+        <v>2.044043309753056</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.087649136379536</v>
+        <v>-7.97229101879079</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.07955841102527028</v>
+        <v>-0.03341516398977173</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.721693444108122</v>
+        <v>-1.606335326519373</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.122841601375419</v>
+        <v>2.192056471928668</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.937982745372021</v>
+        <v>-7.822624627783275</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02258406493522314</v>
+        <v>0.02355918210027497</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.628789952865586</v>
+        <v>-1.513431835276837</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.175691485807981</v>
+        <v>2.244906356361231</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.805707271741134</v>
+        <v>-7.690349154152389</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02569361126415837</v>
+        <v>0.07183685829965647</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.496514479234699</v>
+        <v>-1.381156361645951</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.25042425673354</v>
+        <v>2.31963912728679</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.615107597067982</v>
+        <v>-7.499749479479236</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1047485418210563</v>
+        <v>0.1508917888565544</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.305914804561546</v>
+        <v>-1.190556686972798</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.367599122225069</v>
+        <v>2.436813992778318</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.366107798384401</v>
+        <v>-7.250749680795655</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2172548025181471</v>
+        <v>0.2633980495536457</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.305914804561546</v>
+        <v>-1.190556686972798</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.380505463448728</v>
+        <v>2.449720334001976</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.471697788157505</v>
+        <v>-7.35633967056876</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.0470428770096869</v>
+        <v>0.093186124045185</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.41150479433465</v>
+        <v>-1.296146676745902</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.189175539985647</v>
+        <v>2.258390410538895</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.490432690276102</v>
+        <v>-7.375074572687357</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08809325803933454</v>
+        <v>0.1342365050748326</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.41150479433465</v>
+        <v>-1.296146676745902</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.237719881862733</v>
+        <v>2.306934752415982</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.342492648868503</v>
+        <v>-7.227134531279757</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02739035191420669</v>
+        <v>0.07353359894970479</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.391183878426093</v>
+        <v>-1.275825760837345</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.1300335087197</v>
+        <v>2.199248379272948</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.31826401247953</v>
+        <v>-7.202905894890785</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02836782021631734</v>
+        <v>0.07451106725181544</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.36695524203712</v>
+        <v>-1.251597124448372</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.135856704299605</v>
+        <v>2.205071574852854</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.27471560570884</v>
+        <v>-7.159357488120095</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03882657082950036</v>
+        <v>0.08496981786499846</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.36695524203712</v>
+        <v>-1.251597124448372</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.128896092204512</v>
+        <v>2.19811096275776</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.032567212254982</v>
+        <v>-6.917209094666236</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1501482825921867</v>
+        <v>0.1962915296276848</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.36695524203712</v>
+        <v>-1.251597124448372</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.143358446585655</v>
+        <v>2.212573317138903</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.969337840486634</v>
+        <v>-6.853979722897888</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1699721517587212</v>
+        <v>0.2161153987942193</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.36695524203712</v>
+        <v>-1.251597124448372</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.13789056704485</v>
+        <v>2.207105437598099</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.846046705669503</v>
+        <v>-6.730688588080757</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2167866996961503</v>
+        <v>0.2629299467316484</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.24366410721999</v>
+        <v>-1.128305989631242</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.209363341945705</v>
+        <v>2.278578212498954</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.824897506766059</v>
+        <v>-6.709539389177314</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2329473574948526</v>
+        <v>0.2790906045303512</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.222514908316547</v>
+        <v>-1.107156790727799</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.229753839525096</v>
+        <v>2.298968710078345</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.581132064782615</v>
+        <v>-6.46577394719387</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3262342426352811</v>
+        <v>0.3723774896707792</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.222514908316547</v>
+        <v>-1.107156790727799</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.225534547872147</v>
+        <v>2.294749418425396</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.434235037064745</v>
+        <v>-6.318876919475999</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3871173676424453</v>
+        <v>0.4332606146779439</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.174856666337959</v>
+        <v>-1.059498548749211</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.256253806979315</v>
+        <v>2.325468677532565</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.184384643115671</v>
+        <v>-6.069026525526924</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4797996002057769</v>
+        <v>0.5259428472412755</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.174856666337959</v>
+        <v>-1.059498548749211</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.248995881963018</v>
+        <v>2.318210752516267</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.008492550648239</v>
+        <v>-5.893134433059492</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5537555607133986</v>
+        <v>0.5998988077488971</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.174856666337959</v>
+        <v>-1.059498548749211</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.252595005483666</v>
+        <v>2.321809876036915</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.837046087625775</v>
+        <v>-5.721687970037029</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.635661651976938</v>
+        <v>0.6818048990124366</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.003410203315496</v>
+        <v>-0.8880520857267474</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.368790389351698</v>
+        <v>2.438005259904947</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.612013087956952</v>
+        <v>-5.496654970368206</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7246953294607641</v>
+        <v>0.7708385764962626</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7783772036466728</v>
+        <v>-0.6630190860579246</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.502830666769289</v>
+        <v>2.572045537322538</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.548377345723018</v>
+        <v>-5.433019228134271</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.754844427408655</v>
+        <v>0.8009876744441535</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7147414614127383</v>
+        <v>-0.5993833438239901</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.545706913163967</v>
+        <v>2.614921783717216</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.455377304517119</v>
+        <v>-5.340019186928373</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.77323870267481</v>
+        <v>0.8193819497103085</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7147414614127383</v>
+        <v>-0.5993833438239901</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.526901171947762</v>
+        <v>2.596116042501011</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.214946807712259</v>
+        <v>-5.099588690123513</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8711539780216313</v>
+        <v>0.9172972250571299</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.474310964607878</v>
+        <v>-0.3589528470191298</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.672902546655556</v>
+        <v>2.742117417208805</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.142704239541064</v>
+        <v>-5.027346121952318</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9039803191249294</v>
+        <v>0.9501235661604279</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.474310964607878</v>
+        <v>-0.3589528470191298</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.676831860490376</v>
+        <v>2.746046731043625</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.089705917259677</v>
+        <v>-4.97434779967093</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9258582319548245</v>
+        <v>0.9720014789903233</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4189747056059392</v>
+        <v>-0.3036165880171909</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.71071219980888</v>
+        <v>2.779927070362128</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.98090103177995</v>
+        <v>-4.865542914191203</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.966378257366709</v>
+        <v>1.012521504402208</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4189747056059392</v>
+        <v>-0.3036165880171909</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.707710271028873</v>
+        <v>2.776925141582122</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145931</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.897150497936862</v>
+        <v>-4.645522116154193</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.001457507914558</v>
+        <v>1.102108860627626</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4179286467277993</v>
+        <v>-0.1623967429492107</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.709916943366371</v>
+        <v>2.863236085633524</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.764282808873585</v>
+        <v>-4.512654427090915</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.070498766341692</v>
+        <v>1.17115011905476</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4179286467277993</v>
+        <v>-0.1623967429492107</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.725811126168194</v>
+        <v>2.879130268435347</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.604767705354215</v>
+        <v>-4.353139323571545</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.135450652189742</v>
+        <v>1.23610200490281</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2584135432084294</v>
+        <v>-0.002881639429840765</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.822666032720118</v>
+        <v>2.975985174987271</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.460095560254477</v>
+        <v>-4.208467178471808</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.203407612791077</v>
+        <v>1.304058965504145</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1137413981086919</v>
+        <v>0.1417905056698966</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.9195574223414</v>
+        <v>3.072876564608554</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.51997038761217</v>
+        <v>-4.2683420058295</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.165495173249426</v>
+        <v>1.266146525962494</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1736162254663841</v>
+        <v>0.08191567831220453</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.869670017328211</v>
+        <v>3.022989159595364</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.433170889833161</v>
+        <v>-4.181542508050491</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.222615465683596</v>
+        <v>1.323266818396664</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1736162254663841</v>
+        <v>0.08191567831220453</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.892070510650777</v>
+        <v>3.04538965291793</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.435640596294967</v>
+        <v>-4.184012214512297</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.221699984472286</v>
+        <v>1.322351337185353</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1760859319281902</v>
+        <v>0.07944597185039837</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.890661088147106</v>
+        <v>3.043980230414259</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.504010782618977</v>
+        <v>-4.252382400836307</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.205358832417383</v>
+        <v>1.306010185130451</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1668102328919753</v>
+        <v>0.08872167088661331</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.907233430043537</v>
+        <v>3.060552572310689</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.612548963535111</v>
+        <v>-4.360920581752441</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.152380268682821</v>
+        <v>1.253031621395889</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1668102328919753</v>
+        <v>0.08872167088661331</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.897670138675428</v>
+        <v>3.050989280942581</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.643542122863816</v>
+        <v>-4.391913741081146</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9646925699917257</v>
+        <v>1.065343922704794</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1668102328919753</v>
+        <v>0.08872167088661331</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.722379703715815</v>
+        <v>2.875698845982968</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675893</v>
+        <v>3.746038950675891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.468067863071347</v>
+        <v>-4.216439481288678</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.039449505900501</v>
+        <v>1.140100858613569</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1668102328919753</v>
+        <v>0.08872167088661331</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.726946935707602</v>
+        <v>2.880266077974755</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695439</v>
+        <v>3.765020747695436</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.579004115712596</v>
+        <v>-4.327375733929927</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9708170336052087</v>
+        <v>1.071468386318276</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1668102328919753</v>
+        <v>0.08872167088661331</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.702688964468809</v>
+        <v>2.856008106735962</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.782030693255829</v>
+        <v>-4.53040231147316</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8927377878078209</v>
+        <v>0.9933891405208888</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3698368104352087</v>
+        <v>-0.1143049066566201</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.584004403162775</v>
+        <v>2.737323545429928</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.624105094320536</v>
+        <v>-4.372476712537867</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9660804138140704</v>
+        <v>1.066731766527138</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3698368104352087</v>
+        <v>-0.1143049066566201</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.594176789594907</v>
+        <v>2.747495931862061</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.537861631294159</v>
+        <v>-4.286233249511489</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9955240695984817</v>
+        <v>1.09617542231155</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3698368104352087</v>
+        <v>-0.1143049066566201</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.589123060168768</v>
+        <v>2.742442202435921</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.53904471594522</v>
+        <v>-4.28741633416255</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9868266111825827</v>
+        <v>1.087477963895651</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3754798589017202</v>
+        <v>-0.1199479551231316</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.577513006533386</v>
+        <v>2.730832148800539</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.415917008951137</v>
+        <v>-4.164288627168467</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.036629567013318</v>
+        <v>1.137280919726385</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3754798589017202</v>
+        <v>-0.1199479551231316</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.578064879566488</v>
+        <v>2.731384021833641</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.323106527500277</v>
+        <v>-4.071478145717608</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.003026451485027</v>
+        <v>1.103677804198095</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2826693774508608</v>
+        <v>-0.02713747367227226</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.563023860328369</v>
+        <v>2.716343002595522</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.274543475279247</v>
+        <v>-4.022915093496578</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.02432514829804</v>
+        <v>1.124976501011108</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2341063252298307</v>
+        <v>0.02142557854875793</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.594035167585588</v>
+        <v>2.747354309852741</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.161872257042997</v>
+        <v>-3.910243875260328</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.064469344104263</v>
+        <v>1.165120696817331</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1214351069935805</v>
+        <v>0.1340967967850081</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.656713607039061</v>
+        <v>2.810032749306214</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.049495255860324</v>
+        <v>-3.797866874077655</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.114911440407999</v>
+        <v>1.215562793121067</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1214351069935805</v>
+        <v>0.1340967967850081</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.662204902869728</v>
+        <v>2.815524045136882</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.247729824747055</v>
+        <v>-3.996101442964386</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.047114814621846</v>
+        <v>1.147766167334914</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.319669675880311</v>
+        <v>-0.06413777210172245</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.554761363306229</v>
+        <v>2.708080505573382</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306604617532</v>
+        <v>3.643066046175318</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.330731105772334</v>
+        <v>-4.079102723989664</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8522700222123878</v>
+        <v>0.9529213749254557</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3382405604074848</v>
+        <v>-0.0827086566288962</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.381974552590578</v>
+        <v>2.535293694857731</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199265</v>
+        <v>3.682712735199263</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.457798112079322</v>
+        <v>-4.206169730296653</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9215928804087983</v>
+        <v>1.022244233121866</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3382405604074848</v>
+        <v>-0.0827086566288962</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.502124213309784</v>
+        <v>2.655443355576937</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660763</v>
+        <v>3.733008865660762</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.544396695060425</v>
+        <v>-4.292768313277755</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9014664733186799</v>
+        <v>1.002117826031748</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3382405604074848</v>
+        <v>-0.0827086566288962</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.516637239412107</v>
+        <v>2.66995638167926</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383419</v>
+        <v>3.741170494383417</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.506013032502274</v>
+        <v>-4.254384650719604</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9142393796843091</v>
+        <v>1.014890732397377</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2998568978493336</v>
+        <v>-0.04432499407074503</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.537086878289366</v>
+        <v>2.690406020556519</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114362200248</v>
+        <v>3.751143622002478</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.328896702467108</v>
+        <v>-4.077268320684438</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9818149405436776</v>
+        <v>1.082466293256745</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2998568978493336</v>
+        <v>-0.04432499407074503</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.533815907134668</v>
+        <v>2.687135049401821</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263896</v>
+        <v>3.741324873263895</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.299194578490814</v>
+        <v>-4.047566196708145</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9943791818961081</v>
+        <v>1.095030534609176</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.304327023064647</v>
+        <v>-0.0487951192860584</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.531817223767393</v>
+        <v>2.685136366034546</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481229</v>
+        <v>3.750725801481227</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.119819157252047</v>
+        <v>-3.868190775469377</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.05991632569803</v>
+        <v>1.160567678411097</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1475502648939283</v>
+        <v>0.1079816388846603</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.619670253976239</v>
+        <v>2.772989396243392</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452224</v>
+        <v>3.716988143452222</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.164833370772653</v>
+        <v>-3.913204988989983</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.022718095621377</v>
+        <v>1.123369448334445</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1778991602085329</v>
+        <v>0.07763274357005567</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.582268372119066</v>
+        <v>2.735587514386219</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979531</v>
+        <v>3.737023032979529</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.431837881045088</v>
+        <v>-4.180209499262419</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9216078538513484</v>
+        <v>1.022259206564416</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3722621982514815</v>
+        <v>-0.1167302944728929</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.471342111632242</v>
+        <v>2.624661253899395</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.720625101504003</v>
+        <v>-4.263279073299423</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8052968875642836</v>
+        <v>0.9882352988461158</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4733483183504819</v>
+        <v>-0.1733459654601883</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.409894361469344</v>
+        <v>2.58989577320352</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.70556808628545</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.688149515333231</v>
+        <v>-4.230803487128651</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8158870835869092</v>
+        <v>0.9988254948687414</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4733483183504819</v>
+        <v>-0.1733459654601883</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.40749432302366</v>
+        <v>2.587495734757836</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.669111387625934</v>
+        <v>-4.211765359421354</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8200270538780732</v>
+        <v>1.002965465159905</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5315319296816764</v>
+        <v>-0.2315295767913829</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.369108875433188</v>
+        <v>2.549110287167364</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.700238018776552</v>
+        <v>-4.242891990571972</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9851582703565063</v>
+        <v>1.168096681638338</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5315319296816764</v>
+        <v>-0.2315295767913829</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.546690744371869</v>
+        <v>2.726692156106045</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.752558399377344</v>
+        <v>-4.295212371172764</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9650634471023232</v>
+        <v>1.148001858384155</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4965850696728042</v>
+        <v>-0.1965827167825107</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.568492189363326</v>
+        <v>2.748493601097502</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259119</v>
+        <v>3.787422005259117</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.896881305302263</v>
+        <v>-4.439535277097683</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9133428151292815</v>
+        <v>1.096281226411114</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4965850696728042</v>
+        <v>-0.1965827167825107</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.574500719760252</v>
+        <v>2.754502131494428</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989904</v>
+        <v>3.781497674989902</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.74913833506726</v>
+        <v>-4.29179230686268</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.051592651015304</v>
+        <v>1.234531062297137</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3287777124379211</v>
+        <v>-0.02877535954762755</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.754337781893204</v>
+        <v>2.934339193627379</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651165</v>
+        <v>3.802242353651163</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.851153017598482</v>
+        <v>-4.393806989393902</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.013580399534297</v>
+        <v>1.196518810816129</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3287777124379211</v>
+        <v>-0.02877535954762755</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.757131403424685</v>
+        <v>2.93713281515886</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864724</v>
+        <v>3.805605409864723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.714543673504389</v>
+        <v>-4.257197645299809</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.068886485563592</v>
+        <v>1.251824896845424</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1921683683438286</v>
+        <v>0.1078339845464649</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.839759358272798</v>
+        <v>3.019760770006974</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360612</v>
+        <v>3.79823621936061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.857309006327039</v>
+        <v>-4.399962978122459</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.010860829174643</v>
+        <v>1.193799240456475</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.334933701166479</v>
+        <v>-0.03493134827618549</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.753180635319318</v>
+        <v>2.933182047053494</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268422</v>
+        <v>3.86735906126842</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.795011007550917</v>
+        <v>-4.337664979346337</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.102115582481912</v>
+        <v>1.285053993763744</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.334933701166479</v>
+        <v>-0.03493134827618549</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.819516189116139</v>
+        <v>2.999517600850315</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462185</v>
+        <v>3.848725564462184</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.593220809885759</v>
+        <v>-4.135874781681179</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8914125339373735</v>
+        <v>1.074350945219206</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1369155089973246</v>
+        <v>0.1630868438929689</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.64690797680703</v>
+        <v>2.826909388541206</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322409</v>
+        <v>3.841441242322406</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.533330128243166</v>
+        <v>-4.075984100038585</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.985659038916586</v>
+        <v>1.168597450198418</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.07702482735473115</v>
+        <v>0.2229775255355624</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.753132618114762</v>
+        <v>2.933134029848937</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.776562762395375</v>
+        <v>3.893658111395332</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.745404374078463</v>
+        <v>2.965103308949651</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.533330128243166</v>
+        <v>-4.075984100038585</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.985659038916586</v>
+        <v>1.168597450198418</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.07702482735473115</v>
+        <v>0.2229775255355624</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.738468171064831</v>
+        <v>2.958167105936019</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>57.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-30.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.4%</t>
+          <t>126.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.3%</t>
+          <t>449.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-569.2%</t>
+          <t>-577.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.4%</t>
+          <t>-261.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-247.9%</t>
+          <t>-633.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-201.7%</t>
+          <t>-198.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-150.2%</t>
+          <t>-149.5%</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776673</v>
+        <v>3.500446096776672</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781941</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567235</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487765</v>
+        <v>3.789307536487764</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309719</v>
+        <v>3.833249172309717</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858721</v>
+        <v>3.839370871858719</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096466</v>
+        <v>3.856158176096464</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.205772241020389</v>
+        <v>-8.269144228508811</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1347320817194637</v>
+        <v>-0.1600808767148325</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.839816548748972</v>
+        <v>-1.903188536237395</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.044043309753056</v>
+        <v>2.006020117260003</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.97229101879079</v>
+        <v>-8.035663006279211</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.03341516398977173</v>
+        <v>-0.05876395898514009</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.606335326519373</v>
+        <v>-1.669707314007796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.192056471928668</v>
+        <v>2.154033279435614</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255782</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.822624627783275</v>
+        <v>-7.885996615271696</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.02355918210027497</v>
+        <v>-0.001789612895093384</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.513431835276837</v>
+        <v>-1.57680382276526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.244906356361231</v>
+        <v>2.206883163868177</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.690349154152389</v>
+        <v>-7.75372114164081</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.07183685829965647</v>
+        <v>0.04648806330428812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.381156361645951</v>
+        <v>-1.444528349134373</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.31963912728679</v>
+        <v>2.281615934793736</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.499749479479236</v>
+        <v>-7.563121466967657</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1508917888565544</v>
+        <v>0.1255429938611861</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.190556686972798</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.436813992778318</v>
+        <v>2.398790800285264</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.250749680795655</v>
+        <v>-7.314121668284076</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2633980495536457</v>
+        <v>0.2380492545582773</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.190556686972798</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.449720334001976</v>
+        <v>2.411697141508923</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.35633967056876</v>
+        <v>-7.419711658057181</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.093186124045185</v>
+        <v>0.06783732904981665</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.296146676745902</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.258390410538895</v>
+        <v>2.220367218045842</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457896</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.375074572687357</v>
+        <v>-7.438446560175778</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1342365050748326</v>
+        <v>0.1088877100794643</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.296146676745902</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.306934752415982</v>
+        <v>2.268911559922928</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.227134531279757</v>
+        <v>-7.290506518768178</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.07353359894970479</v>
+        <v>0.04818480395433644</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.275825760837345</v>
+        <v>-1.339197748325767</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.199248379272948</v>
+        <v>2.161225186779895</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879198</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.202905894890785</v>
+        <v>-7.266277882379206</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.07451106725181544</v>
+        <v>0.04916227225644709</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.251597124448372</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.205071574852854</v>
+        <v>2.1670483823598</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.159357488120095</v>
+        <v>-7.222729475608515</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08496981786499846</v>
+        <v>0.05962102286963011</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.251597124448372</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.19811096275776</v>
+        <v>2.160087770264707</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.917209094666236</v>
+        <v>-6.980581082154657</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1962915296276848</v>
+        <v>0.1709427346323165</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.251597124448372</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.212573317138903</v>
+        <v>2.17455012464585</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.853979722897888</v>
+        <v>-6.917351710386309</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2161153987942193</v>
+        <v>0.1907666037988509</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.251597124448372</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.207105437598099</v>
+        <v>2.169082245105045</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.730688588080757</v>
+        <v>-6.794060575569178</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2629299467316484</v>
+        <v>0.23758115173628</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.128305989631242</v>
+        <v>-1.191677977119665</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.278578212498954</v>
+        <v>2.2405550200059</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.709539389177314</v>
+        <v>-6.772911376665735</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2790906045303512</v>
+        <v>0.2537418095349828</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.107156790727799</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.298968710078345</v>
+        <v>2.260945517585291</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.46577394719387</v>
+        <v>-6.52914593468229</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3723774896707792</v>
+        <v>0.3470286946754109</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.107156790727799</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.294749418425396</v>
+        <v>2.256726225932342</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.318876919475999</v>
+        <v>-6.382248906964421</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4332606146779439</v>
+        <v>0.4079118196825751</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.059498548749211</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.325468677532565</v>
+        <v>2.287445485039511</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749179</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.069026525526924</v>
+        <v>-6.132398513015346</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5259428472412755</v>
+        <v>0.5005940522459071</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.059498548749211</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.318210752516267</v>
+        <v>2.280187560023213</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.893134433059492</v>
+        <v>-5.956506420547914</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5998988077488971</v>
+        <v>0.5745500127535288</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.059498548749211</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.321809876036915</v>
+        <v>2.283786683543862</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.721687970037029</v>
+        <v>-5.78505995752545</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6818048990124366</v>
+        <v>0.6564561040170678</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8880520857267474</v>
+        <v>-0.9514240732151701</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.438005259904947</v>
+        <v>2.399982067411893</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102774</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.496654970368206</v>
+        <v>-5.560026957856627</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7708385764962626</v>
+        <v>0.7454897815008938</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.6630190860579246</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.572045537322538</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.764614304353066</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.433019228134271</v>
+        <v>-5.496391215622693</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8009876744441535</v>
+        <v>0.7756388794487847</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5993833438239901</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.614921783717216</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544775</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.340019186928373</v>
+        <v>-5.403391174416795</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8193819497103085</v>
+        <v>0.7940331547149397</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5993833438239901</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.596116042501011</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712285</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.099588690123513</v>
+        <v>-5.162960677611935</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9172972250571299</v>
+        <v>0.8919484300617615</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3589528470191298</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.742117417208805</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837675</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.027346121952318</v>
+        <v>-5.09071810944074</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9501235661604279</v>
+        <v>0.9247747711650596</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3589528470191298</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.746046731043625</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.822323422349957</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.97434779967093</v>
+        <v>-5.037719787159352</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9720014789903233</v>
+        <v>0.9466526839949547</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3036165880171909</v>
+        <v>-0.3669885755056136</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.779927070362128</v>
+        <v>2.741903877869075</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.848613050972331</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.865542914191203</v>
+        <v>-4.928914901679625</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.012521504402208</v>
+        <v>0.9871727094068388</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3036165880171909</v>
+        <v>-0.3669885755056136</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.776925141582122</v>
+        <v>2.738901949089068</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.81866537614593</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.645522116154193</v>
+        <v>-4.708894103642614</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.102108860627626</v>
+        <v>1.076760065632257</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1623967429492107</v>
+        <v>-0.2257687304376333</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.863236085633524</v>
+        <v>2.825212893140471</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009943</v>
+        <v>3.843270952009942</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.512654427090915</v>
+        <v>-4.576026414579337</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.17115011905476</v>
+        <v>1.145801324059392</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1623967429492107</v>
+        <v>-0.2257687304376333</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.879130268435347</v>
+        <v>2.841107075942294</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.353139323571545</v>
+        <v>-4.416511311059967</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.23610200490281</v>
+        <v>1.210753209907441</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.002881639429840765</v>
+        <v>-0.06625362691826342</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.975985174987271</v>
+        <v>2.937961982494218</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.208467178471808</v>
+        <v>-4.27183916596023</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.304058965504145</v>
+        <v>1.278710170508776</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1417905056698966</v>
+        <v>0.078418518181474</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.072876564608554</v>
+        <v>3.0348533721155</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.2683420058295</v>
+        <v>-4.331713993317922</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.266146525962494</v>
+        <v>1.240797730967125</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.08191567831220453</v>
+        <v>0.01854369082378188</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.022989159595364</v>
+        <v>2.984965967102311</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.181542508050491</v>
+        <v>-4.244914495538913</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.323266818396664</v>
+        <v>1.297918023401295</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.08191567831220453</v>
+        <v>0.01854369082378188</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.04538965291793</v>
+        <v>3.007366460424877</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.184012214512297</v>
+        <v>-4.247384202000719</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.322351337185353</v>
+        <v>1.297002542189985</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.07944597185039837</v>
+        <v>0.01607398436197571</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.043980230414259</v>
+        <v>3.005957037921205</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.252382400836307</v>
+        <v>-4.315754388324729</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.306010185130451</v>
+        <v>1.280661390135083</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.08872167088661331</v>
+        <v>0.02534968339819066</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.060552572310689</v>
+        <v>3.022529379817636</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.360920581752441</v>
+        <v>-4.424292569240863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.253031621395889</v>
+        <v>1.22768282640052</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.08872167088661331</v>
+        <v>0.02534968339819066</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.050989280942581</v>
+        <v>3.012966088449527</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.391913741081146</v>
+        <v>-4.455285728569568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.065343922704794</v>
+        <v>1.039995127709425</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.08872167088661331</v>
+        <v>0.02534968339819066</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.875698845982968</v>
+        <v>2.837675653489914</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.216439481288678</v>
+        <v>-4.279811468777099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.140100858613569</v>
+        <v>1.1147520636182</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.08872167088661331</v>
+        <v>0.02534968339819066</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.880266077974755</v>
+        <v>2.842242885481702</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.327375733929927</v>
+        <v>-4.390747721418348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.071468386318276</v>
+        <v>1.046119591322908</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.08872167088661331</v>
+        <v>0.02534968339819066</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.856008106735962</v>
+        <v>2.817984914242909</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.53040231147316</v>
+        <v>-4.593774298961582</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9933891405208888</v>
+        <v>0.96804034552552</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1143049066566201</v>
+        <v>-0.1776768941450427</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.737323545429928</v>
+        <v>2.699300352936874</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.372476712537867</v>
+        <v>-4.435848700026289</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.066731766527138</v>
+        <v>1.04138297153177</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1143049066566201</v>
+        <v>-0.1776768941450427</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.747495931862061</v>
+        <v>2.709472739369007</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.286233249511489</v>
+        <v>-4.349605236999911</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.09617542231155</v>
+        <v>1.070826627316181</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1143049066566201</v>
+        <v>-0.1776768941450427</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.742442202435921</v>
+        <v>2.704419009942867</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.28741633416255</v>
+        <v>-4.350788321650972</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.087477963895651</v>
+        <v>1.062129168900282</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1199479551231316</v>
+        <v>-0.1833199426115543</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.730832148800539</v>
+        <v>2.692808956307486</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.164288627168467</v>
+        <v>-4.227660614656889</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.137280919726385</v>
+        <v>1.111932124731017</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1199479551231316</v>
+        <v>-0.1833199426115543</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.731384021833641</v>
+        <v>2.693360829340588</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.071478145717608</v>
+        <v>-4.134850133206029</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.103677804198095</v>
+        <v>1.078329009202726</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.02713747367227226</v>
+        <v>-0.09050946116069492</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.716343002595522</v>
+        <v>2.678319810102469</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.022915093496578</v>
+        <v>-4.086287080985</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.124976501011108</v>
+        <v>1.099627706015739</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.02142557854875793</v>
+        <v>-0.04194640893966473</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.747354309852741</v>
+        <v>2.709331117359687</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.910243875260328</v>
+        <v>-3.973615862748749</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.165120696817331</v>
+        <v>1.139771901821962</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1340967967850081</v>
+        <v>0.07072480929658548</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.810032749306214</v>
+        <v>2.772009556813161</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.797866874077655</v>
+        <v>-3.861238861566077</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.215562793121067</v>
+        <v>1.190213998125698</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1340967967850081</v>
+        <v>0.07072480929658548</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.815524045136882</v>
+        <v>2.777500852643828</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.996101442964386</v>
+        <v>-4.059473430452807</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.147766167334914</v>
+        <v>1.122417372339545</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.06413777210172245</v>
+        <v>-0.1275097595901451</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.708080505573382</v>
+        <v>2.670057313080329</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.079102723989664</v>
+        <v>-4.142474711478086</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9529213749254557</v>
+        <v>0.9275725799300869</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.0827086566288962</v>
+        <v>-0.1460806441173189</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.535293694857731</v>
+        <v>2.497270502364678</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.206169730296653</v>
+        <v>-4.269541717785074</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.022244233121866</v>
+        <v>0.9968954381264974</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.0827086566288962</v>
+        <v>-0.1460806441173189</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.655443355576937</v>
+        <v>2.617420163083883</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.292768313277755</v>
+        <v>-4.356140300766177</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.002117826031748</v>
+        <v>0.9767690310363792</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.0827086566288962</v>
+        <v>-0.1460806441173189</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.66995638167926</v>
+        <v>2.631933189186206</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.254384650719604</v>
+        <v>-4.317756638208026</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.014890732397377</v>
+        <v>0.9895419374020082</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.04432499407074503</v>
+        <v>-0.1076969815591677</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.690406020556519</v>
+        <v>2.652382828063466</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.077268320684438</v>
+        <v>-4.14064030817286</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.082466293256745</v>
+        <v>1.057117498261377</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.04432499407074503</v>
+        <v>-0.1076969815591677</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.687135049401821</v>
+        <v>2.649111856908767</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.047566196708145</v>
+        <v>-4.110938184196566</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.095030534609176</v>
+        <v>1.069681739613807</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.0487951192860584</v>
+        <v>-0.1121671067744811</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.685136366034546</v>
+        <v>2.647113173541493</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.868190775469377</v>
+        <v>-3.931562762957799</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.160567678411097</v>
+        <v>1.135218883415729</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1079816388846603</v>
+        <v>0.04460965139623763</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772989396243392</v>
+        <v>2.734966203750338</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.913204988989983</v>
+        <v>-3.976576976478405</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.123369448334445</v>
+        <v>1.098020653339076</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.07763274357005567</v>
+        <v>0.01426075608163302</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.735587514386219</v>
+        <v>2.697564321893165</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.180209499262419</v>
+        <v>-4.24358148675084</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.022259206564416</v>
+        <v>0.9969104115690475</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1167302944728929</v>
+        <v>-0.1801022819613156</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.624661253899395</v>
+        <v>2.586638061406342</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.263279073299423</v>
+        <v>-4.33974652927846</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9882352988461158</v>
+        <v>0.9576483164545011</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1733459654601883</v>
+        <v>-0.2492195091102749</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.58989577320352</v>
+        <v>2.544371647013468</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.230803487128651</v>
+        <v>-4.307270943107688</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9988254948687414</v>
+        <v>0.9682385124771267</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1733459654601883</v>
+        <v>-0.2492195091102749</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.587495734757836</v>
+        <v>2.541971608567784</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.211765359421354</v>
+        <v>-4.288232815400391</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.002965465159905</v>
+        <v>0.9723784827682904</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2315295767913829</v>
+        <v>-0.3074031204414694</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.549110287167364</v>
+        <v>2.503586160977313</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.242891990571972</v>
+        <v>-4.319359446551009</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.168096681638338</v>
+        <v>1.137509699246724</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2315295767913829</v>
+        <v>-0.3074031204414694</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.726692156106045</v>
+        <v>2.681168029915993</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.295212371172764</v>
+        <v>-4.371679827151801</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.148001858384155</v>
+        <v>1.11741487599254</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.1965827167825107</v>
+        <v>-0.2724562604325973</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.748493601097502</v>
+        <v>2.70296947490745</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.439535277097683</v>
+        <v>-4.51600273307672</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.096281226411114</v>
+        <v>1.065694244019499</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.1965827167825107</v>
+        <v>-0.2724562604325973</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.754502131494428</v>
+        <v>2.708978005304376</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.29179230686268</v>
+        <v>-4.368259762841717</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.234531062297137</v>
+        <v>1.203944079905522</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.02877535954762755</v>
+        <v>-0.1046489031977141</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.934339193627379</v>
+        <v>2.888815067437328</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.393806989393902</v>
+        <v>-4.470274445372938</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.196518810816129</v>
+        <v>1.165931828424514</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.02877535954762755</v>
+        <v>-0.1046489031977141</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.93713281515886</v>
+        <v>2.891608688968809</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.257197645299809</v>
+        <v>-4.333665101278846</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.251824896845424</v>
+        <v>1.22123791445381</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1078339845464649</v>
+        <v>0.03196044089637834</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.019760770006974</v>
+        <v>2.974236643816922</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.399962978122459</v>
+        <v>-4.371004446303539</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.193799240456475</v>
+        <v>1.205382653184043</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.03493134827618549</v>
+        <v>-0.00537890412831471</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.933182047053494</v>
+        <v>2.950913513542217</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.337664979346337</v>
+        <v>-4.308706447527417</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.285053993763744</v>
+        <v>1.296637406491312</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.03493134827618549</v>
+        <v>-0.00537890412831471</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.999517600850315</v>
+        <v>3.017249067339038</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.135874781681179</v>
+        <v>-4.106916249862259</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.074350945219206</v>
+        <v>1.085934357946774</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1630868438929689</v>
+        <v>0.1926392880408397</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.826909388541206</v>
+        <v>2.844640855029929</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322406</v>
+        <v>3.841441242322407</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.075984100038585</v>
+        <v>-4.047025568219666</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.168597450198418</v>
+        <v>1.180180862925986</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2229775255355624</v>
+        <v>0.2525299696834332</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.933134029848937</v>
+        <v>2.95086549633766</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.893658111395332</v>
+        <v>3.858503961719051</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.965103308949651</v>
+        <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.075984100038585</v>
+        <v>-4.15804098408427</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.168597450198418</v>
+        <v>1.150402432696188</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.2229775255355624</v>
+        <v>0.2525299696834332</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.958167105936019</v>
+        <v>2.965493232453703</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240523.xlsx
+++ b/tame_output/ON/bt/strategyON_20240523.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>30.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.3%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.1%</t>
+          <t>446.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-577.4%</t>
+          <t>-606.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-261.2%</t>
+          <t>-272.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-633.3%</t>
+          <t>-68.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-198.7%</t>
+          <t>-209.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-149.5%</t>
+          <t>-156.1%</t>
         </is>
       </c>
     </row>
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612275</v>
+        <v>3.346417924612274</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705544</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279816</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255782</v>
+        <v>3.801633547255781</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860422</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077639</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457895</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180804</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.723562653879197</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568102</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963413</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192811</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749179</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481491</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.78093033586298</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353066</v>
+        <v>3.764614304353065</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544775</v>
+        <v>3.798811195544774</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.416511311059967</v>
+        <v>-4.506710080563502</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.210753209907441</v>
+        <v>1.174673702106027</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06625362691826342</v>
+        <v>-0.1564523964217985</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.937961982494218</v>
+        <v>2.883842720792097</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.27183916596023</v>
+        <v>-4.362037935463764</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.278710170508776</v>
+        <v>1.242630662707362</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.078418518181474</v>
+        <v>-0.01178025132206112</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.0348533721155</v>
+        <v>2.980734110413379</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.331713993317922</v>
+        <v>-4.421912762821457</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.240797730967125</v>
+        <v>1.204718223165711</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.01854369082378188</v>
+        <v>-0.07165507867975324</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.984965967102311</v>
+        <v>2.93084670540019</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.244914495538913</v>
+        <v>-4.335113265042448</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.297918023401295</v>
+        <v>1.261838515599881</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.01854369082378188</v>
+        <v>-0.07165507867975324</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.007366460424877</v>
+        <v>2.953247198722756</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.247384202000719</v>
+        <v>-4.337582971504254</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.297002542189985</v>
+        <v>1.26092303438857</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.01607398436197571</v>
+        <v>-0.0741247851415594</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.005957037921205</v>
+        <v>2.951837776219084</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.315754388324729</v>
+        <v>-4.405953157828264</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.280661390135083</v>
+        <v>1.244581882333668</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.06484908610534446</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.022529379817636</v>
+        <v>2.968410118115515</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.424292569240863</v>
+        <v>-4.514491338744398</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.22768282640052</v>
+        <v>1.191603318599106</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.06484908610534446</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.012966088449527</v>
+        <v>2.958846826747406</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887696</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.455285728569568</v>
+        <v>-4.545484498073104</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.039995127709425</v>
+        <v>1.003915619908011</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.06484908610534446</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.837675653489914</v>
+        <v>2.783556391787793</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.74603895067589</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.279811468777099</v>
+        <v>-4.370010238280635</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.1147520636182</v>
+        <v>1.078672555816786</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.06484908610534446</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.842242885481702</v>
+        <v>2.788123623779581</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.390747721418348</v>
+        <v>-4.480946490921884</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.046119591322908</v>
+        <v>1.010040083521494</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02534968339819066</v>
+        <v>-0.06484908610534446</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.817984914242909</v>
+        <v>2.763865652540788</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.593774298961582</v>
+        <v>-4.683973068465117</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.96804034552552</v>
+        <v>0.9319608377241058</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1776768941450427</v>
+        <v>-0.2678756636485778</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.699300352936874</v>
+        <v>2.645181091234754</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.435848700026289</v>
+        <v>-4.526047469529824</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.04138297153177</v>
+        <v>1.005303463730355</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1776768941450427</v>
+        <v>-0.2678756636485778</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.709472739369007</v>
+        <v>2.655353477666886</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.349605236999911</v>
+        <v>-4.439804006503446</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.070826627316181</v>
+        <v>1.034747119514767</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1776768941450427</v>
+        <v>-0.2678756636485778</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.704419009942867</v>
+        <v>2.650299748240746</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.350788321650972</v>
+        <v>-4.440987091154508</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.062129168900282</v>
+        <v>1.026049661098868</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1833199426115543</v>
+        <v>-0.2735187121150894</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.692808956307486</v>
+        <v>2.638689694605365</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.227660614656889</v>
+        <v>-4.317859384160425</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.111932124731017</v>
+        <v>1.075852616929603</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1833199426115543</v>
+        <v>-0.2735187121150894</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.693360829340588</v>
+        <v>2.639241567638466</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.134850133206029</v>
+        <v>-4.225048902709565</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.078329009202726</v>
+        <v>1.042249501401312</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.09050946116069492</v>
+        <v>-0.18070823066423</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.678319810102469</v>
+        <v>2.624200548400347</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.086287080985</v>
+        <v>-4.176485850488535</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.099627706015739</v>
+        <v>1.063548198214325</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.04194640893966473</v>
+        <v>-0.1321451784431998</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.709331117359687</v>
+        <v>2.655211855657567</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.973615862748749</v>
+        <v>-4.063814632252285</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.139771901821962</v>
+        <v>1.103692394020548</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07072480929658548</v>
+        <v>-0.01947396020694964</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.772009556813161</v>
+        <v>2.71789029511104</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268532</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.861238861566077</v>
+        <v>-3.951437631069612</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.190213998125698</v>
+        <v>1.154134490324284</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07072480929658548</v>
+        <v>-0.01947396020694964</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.777500852643828</v>
+        <v>2.723381590941707</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.689594264968857</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.059473430452807</v>
+        <v>-4.149672199956343</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.122417372339545</v>
+        <v>1.086337864538131</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1275097595901451</v>
+        <v>-0.2177085290936802</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.670057313080329</v>
+        <v>2.615938051378207</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175318</v>
+        <v>3.643066046175317</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.142474711478086</v>
+        <v>-4.232673480981622</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9275725799300869</v>
+        <v>0.8914930721286727</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1460806441173189</v>
+        <v>-0.236279413620854</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.497270502364678</v>
+        <v>2.443151240662556</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199263</v>
+        <v>3.682712735199261</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.269541717785074</v>
+        <v>-4.35974048728861</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9968954381264974</v>
+        <v>0.9608159303250832</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1460806441173189</v>
+        <v>-0.236279413620854</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.617420163083883</v>
+        <v>2.563300901381762</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660762</v>
+        <v>3.73300886566076</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.356140300766177</v>
+        <v>-4.446339070269713</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9767690310363792</v>
+        <v>0.940689523234965</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1460806441173189</v>
+        <v>-0.236279413620854</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.631933189186206</v>
+        <v>2.577813927484085</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383417</v>
+        <v>3.741170494383415</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.317756638208026</v>
+        <v>-4.407955407711562</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9895419374020082</v>
+        <v>0.953462429600594</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1076969815591677</v>
+        <v>-0.1978957510627028</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.652382828063466</v>
+        <v>2.598263566361345</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002478</v>
+        <v>3.751143622002476</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.14064030817286</v>
+        <v>-4.230839077676396</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.057117498261377</v>
+        <v>1.021037990459962</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1076969815591677</v>
+        <v>-0.1978957510627028</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.649111856908767</v>
+        <v>2.594992595206647</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263895</v>
+        <v>3.741324873263893</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.110938184196566</v>
+        <v>-4.201136953700102</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.069681739613807</v>
+        <v>1.033602231812393</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1121671067744811</v>
+        <v>-0.2023658762780162</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.647113173541493</v>
+        <v>2.592993911839371</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481227</v>
+        <v>3.750725801481225</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.931562762957799</v>
+        <v>-4.021761532461334</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.135218883415729</v>
+        <v>1.099139375614314</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04460965139623763</v>
+        <v>-0.04558911810729749</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.734966203750338</v>
+        <v>2.680846942048217</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452222</v>
+        <v>3.716988143452221</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.976576976478405</v>
+        <v>-4.066775745981941</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.098020653339076</v>
+        <v>1.061941145537662</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01426075608163302</v>
+        <v>-0.0759380134219021</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.697564321893165</v>
+        <v>2.643445060191044</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.737023032979527</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.24358148675084</v>
+        <v>-4.333780256254376</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9969104115690475</v>
+        <v>0.9608309037676332</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1801022819613156</v>
+        <v>-0.2703010514648507</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.586638061406342</v>
+        <v>2.532518799704221</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230803</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.33974652927846</v>
+        <v>-4.622567476713291</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9576483164545011</v>
+        <v>0.8445199374805685</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2492195091102749</v>
+        <v>-0.371387171563851</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.544371647013468</v>
+        <v>2.471071049541322</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285449</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.307270943107688</v>
+        <v>-4.6979569980912</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9682385124771267</v>
+        <v>0.8119640904837215</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2492195091102749</v>
+        <v>-0.371387171563851</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.541971608567784</v>
+        <v>2.468671011095639</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.709506867848096</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.288232815400391</v>
+        <v>-4.678918870383903</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9723784827682904</v>
+        <v>0.8161040607748855</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3074031204414694</v>
+        <v>-0.4295707828950456</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.503586160977313</v>
+        <v>2.430285563505167</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.319359446551009</v>
+        <v>-4.710045501534522</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.137509699246724</v>
+        <v>0.9812352772533186</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3074031204414694</v>
+        <v>-0.4295707828950456</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.681168029915993</v>
+        <v>2.607867432443848</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537861</v>
+        <v>3.722443786537859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.371679827151801</v>
+        <v>-4.762365882135313</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.11741487599254</v>
+        <v>0.9611404539991355</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2724562604325973</v>
+        <v>-0.3946239228861734</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.70296947490745</v>
+        <v>2.629668877435304</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259117</v>
+        <v>3.787422005259115</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.51600273307672</v>
+        <v>-4.906688788060232</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.065694244019499</v>
+        <v>0.9094198220260938</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2724562604325973</v>
+        <v>-0.3946239228861734</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.708978005304376</v>
+        <v>2.63567740783223</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989902</v>
+        <v>3.7814976749899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.368259762841717</v>
+        <v>-4.75894581782523</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.203944079905522</v>
+        <v>1.047669657912117</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1046489031977141</v>
+        <v>-0.2268165656512903</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.888815067437328</v>
+        <v>2.815514469965182</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651163</v>
+        <v>3.802242353651161</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.470274445372938</v>
+        <v>-4.860960500356451</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.165931828424514</v>
+        <v>1.009657406431109</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1046489031977141</v>
+        <v>-0.2268165656512903</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.891608688968809</v>
+        <v>2.818308091496663</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864723</v>
+        <v>3.80560540986472</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.333665101278846</v>
+        <v>-4.724351156262358</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.22123791445381</v>
+        <v>1.064963492460405</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.03196044089637834</v>
+        <v>-0.09020722155719779</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.974236643816922</v>
+        <v>2.900936046344777</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823621936061</v>
+        <v>3.798236219360606</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.371004446303539</v>
+        <v>-4.867116489085008</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.205382653184043</v>
+        <v>1.006937836071455</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.00537890412831471</v>
+        <v>-0.2329725543798482</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.950913513542217</v>
+        <v>2.814357323391297</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86735906126842</v>
+        <v>3.867359061268418</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.308706447527417</v>
+        <v>-4.804818490308886</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.296637406491312</v>
+        <v>1.098192589378725</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.00537890412831471</v>
+        <v>-0.2329725543798482</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.017249067339038</v>
+        <v>2.880692877188118</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462184</v>
+        <v>3.848725564462182</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.106916249862259</v>
+        <v>-4.603028292643728</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.085934357946774</v>
+        <v>0.8874895408341859</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1926392880408397</v>
+        <v>-0.03495436221069381</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.844640855029929</v>
+        <v>2.708084664879008</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322407</v>
+        <v>3.841441242322406</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.047025568219666</v>
+        <v>-4.543137611001135</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.180180862925986</v>
+        <v>0.9817360458133986</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2525299696834332</v>
+        <v>0.02493631943189967</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.95086549633766</v>
+        <v>2.81430930618674</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.858503961719051</v>
+        <v>3.58507710170927</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.15804098408427</v>
+        <v>-4.449189239748262</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.150402432696188</v>
+        <v>1.033943130430591</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.2525299696834332</v>
+        <v>0.1429455688791414</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.965493232453703</v>
+        <v>2.899742591971128</v>
       </c>
     </row>
   </sheetData>
